--- a/yougo.xlsx
+++ b/yougo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\Beat Saber\MAIN\GitHub\bs-jpmapping-glossary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{729357BF-96BD-40DB-8251-0120774D493E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2995EC72-6235-4130-9D4A-04166F85F4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1428" yWindow="1560" windowWidth="24060" windowHeight="21936" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7984,11 +7984,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ノーツが出現する位置からプレイヤーまでの距離。
-＝JD、HJD</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>マッパーの行った音取りやパターン配置など特定の選択に対し、音楽性や一貫性、セットアップやコンテキストなどの観点から、その妥当性を示すこと。奇抜なアイデアでも、それが妥当である理由がきちんと譜面にある（伝わる）ならば、それは正当化できると言える。
 主に譜面のレビューや、ランク化の為のModdingで用いられる言葉であり、言葉通りの意味である。</t>
     <rPh sb="5" eb="6">
@@ -9735,6 +9730,11 @@
     <rPh sb="144" eb="146">
       <t>カンレン</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ノーツが出現する位置からプレイヤーまでの距離。
+＝JD</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -9880,7 +9880,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -10343,7 +10343,7 @@
         <v>248</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="7" t="s">
@@ -10367,7 +10367,7 @@
         <v>255</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="7" t="s">
@@ -10428,7 +10428,7 @@
         <v>20</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>21</v>
@@ -10514,7 +10514,7 @@
         <v>27</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>390</v>
@@ -10538,7 +10538,7 @@
         <v>29</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>391</v>
@@ -10760,7 +10760,7 @@
         <v>46</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>319</v>
@@ -10784,7 +10784,7 @@
         <v>48</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>393</v>
@@ -11094,7 +11094,7 @@
         <v>66</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>404</v>
@@ -11496,7 +11496,7 @@
         <v>542</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>625</v>
@@ -11518,7 +11518,7 @@
         <v>546</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>92</v>
@@ -11606,7 +11606,7 @@
         <v>96</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>97</v>
@@ -11626,7 +11626,7 @@
         <v>98</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>99</v>
@@ -11758,7 +11758,7 @@
         <v>109</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>421</v>
@@ -11782,7 +11782,7 @@
         <v>110</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>422</v>
@@ -11916,7 +11916,7 @@
         <v>117</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>427</v>
@@ -11982,7 +11982,7 @@
         <v>122</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>428</v>
@@ -12004,7 +12004,7 @@
         <v>123</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>429</v>
@@ -12252,7 +12252,7 @@
         <v>138</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>781</v>
+        <v>830</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>439</v>
@@ -12424,7 +12424,7 @@
         <v>149</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>446</v>
@@ -12602,7 +12602,7 @@
         <v>160</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>452</v>
@@ -12624,7 +12624,7 @@
         <v>161</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>453</v>
@@ -12646,7 +12646,7 @@
         <v>162</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>454</v>
@@ -12668,7 +12668,7 @@
         <v>163</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="D113" s="3" t="s">
         <v>455</v>
@@ -12866,7 +12866,7 @@
         <v>176</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="D122" s="3" t="s">
         <v>177</v>
@@ -12980,7 +12980,7 @@
         <v>183</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="D127" s="3" t="s">
         <v>461</v>
@@ -13024,7 +13024,7 @@
         <v>186</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D129" s="3" t="s">
         <v>463</v>
@@ -13046,7 +13046,7 @@
         <v>187</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D130" s="3" t="s">
         <v>624</v>
@@ -13128,7 +13128,7 @@
         <v>192</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="D134" s="3" t="s">
         <v>345</v>
@@ -13172,7 +13172,7 @@
         <v>723</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="D136" s="3" t="s">
         <v>746</v>
@@ -13194,7 +13194,7 @@
         <v>193</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D137" s="3" t="s">
         <v>467</v>
@@ -13218,7 +13218,7 @@
         <v>194</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="D138" s="3" t="s">
         <v>468</v>
@@ -13240,7 +13240,7 @@
         <v>195</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D139" s="3" t="s">
         <v>346</v>
@@ -13530,7 +13530,7 @@
         <v>479</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D152" s="3" t="s">
         <v>478</v>
@@ -13572,7 +13572,7 @@
         <v>210</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="D154" s="3" t="s">
         <v>480</v>
@@ -13910,7 +13910,7 @@
         <v>730</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="D169" s="3" t="s">
         <v>397</v>
@@ -13921,7 +13921,7 @@
       <c r="F169" s="3"/>
       <c r="G169" s="3"/>
       <c r="H169" s="8" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="124.2">
@@ -14000,7 +14000,7 @@
         <v>229</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D173" s="3" t="s">
         <v>43</v>
@@ -14066,7 +14066,7 @@
         <v>231</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D176" s="3" t="s">
         <v>492</v>
@@ -14088,7 +14088,7 @@
         <v>232</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="D177" s="3" t="s">
         <v>493</v>
@@ -14218,7 +14218,7 @@
         <v>724</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D183" s="3" t="s">
         <v>371</v>
@@ -14440,7 +14440,7 @@
         <v>688</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="D193" s="3" t="s">
         <v>558</v>
@@ -14484,7 +14484,7 @@
         <v>608</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="D195" s="3" t="s">
         <v>610</v>
@@ -14572,7 +14572,7 @@
         <v>648</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D199" s="3" t="s">
         <v>662</v>
@@ -14594,7 +14594,7 @@
         <v>649</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="D200" s="3" t="s">
         <v>663</v>
@@ -14752,7 +14752,7 @@
         <v>654</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="D207" s="3" t="s">
         <v>668</v>
@@ -14761,7 +14761,7 @@
         <v>669</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="G207" s="3" t="s">
         <v>536</v>
@@ -14800,7 +14800,7 @@
         <v>658</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D209" s="3" t="s">
         <v>672</v>
@@ -14813,7 +14813,7 @@
         <v>536</v>
       </c>
       <c r="H209" s="8" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="210" spans="1:8" ht="27.6">
@@ -14890,7 +14890,7 @@
         <v>692</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="D213" s="3" t="s">
         <v>694</v>
@@ -15252,7 +15252,7 @@
     </row>
     <row r="6" spans="2:2">
       <c r="B6" s="10" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
   </sheetData>

--- a/yougo.xlsx
+++ b/yougo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\Beat Saber\MAIN\GitHub\bs-jpmapping-glossary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2995EC72-6235-4130-9D4A-04166F85F4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41704D08-1813-408A-A011-BD7C96CF007B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1428" yWindow="1560" windowWidth="24060" windowHeight="21936" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9540" yWindow="4860" windowWidth="24972" windowHeight="19140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="公開用データ" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="831">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1127" uniqueCount="844">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -9735,6 +9735,247 @@
   <si>
     <t>ノーツが出現する位置からプレイヤーまでの距離。
 ＝JD</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スイッチバック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スパイラル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Kizuスライダー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キズスライダー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Kizu slider</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Switch-back</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Spiral</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>kizu</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>spiral</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>switchback</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>曲線の頂点で切り返すプードル配置。
+切り返しの為に、頂点周辺は必ずドットノーツで配置される。角度点を失わせない為にアークが追加される場合も。</t>
+    <rPh sb="0" eb="2">
+      <t>キョクセン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>チョウテン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>タメ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>チョウテン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>シュウヘン</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>カナラ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>カクド</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>ウシナ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>タメ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「螺旋状」を意味する。譜面においては螺旋状に配置された一連のパターンを指す。
+螺旋状に配置され腕をぐるぐる回すスライダーやプードル、螺旋状に配置されたバイブロやストリームなどなど。それぞれを指してスパイラル◯◯とも呼ばれる。
+関連: ボムスパイラル</t>
+    <rPh sb="1" eb="4">
+      <t>ラセンジョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イミ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>フメン</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>ラセ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>イチレン</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="39" eb="42">
+      <t>ラ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="66" eb="69">
+      <t>ラセン</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="95" eb="96">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="107" eb="108">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="113" eb="115">
+      <t>カンレン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>途中で切り返すスライダー配置。
+直線的に切り返すものもあれば、円を描きながら途中で切り返すようなものもある。切り返しの為に、通常のスライダーよりも遅いスロースライダーで配置されることが多い。
+マッパーのkizuflux氏が多用していたことでそう呼ばれるようになったと思われる。
+※画像は一例で、始まりと終わりを矢印ノーツにしたり、2回切り返すなどバリエーションは様々</t>
+    <rPh sb="0" eb="2">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>チョクセン</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>エン</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>タメ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>ツウジョウ</t>
+    </rPh>
+    <rPh sb="73" eb="74">
+      <t>オソ</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="92" eb="93">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="140" eb="142">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="143" eb="145">
+      <t>イチレイ</t>
+    </rPh>
+    <rPh sb="147" eb="148">
+      <t>ハジ</t>
+    </rPh>
+    <rPh sb="151" eb="152">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="155" eb="157">
+      <t>ヤジルシ</t>
+    </rPh>
+    <rPh sb="166" eb="167">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="167" eb="168">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="169" eb="170">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="181" eb="183">
+      <t>サマザマ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -14976,40 +15217,74 @@
         <v>737</v>
       </c>
     </row>
-    <row r="217" spans="1:8">
+    <row r="217" spans="1:8" ht="41.4">
       <c r="A217" s="1">
         <v>216</v>
       </c>
-      <c r="B217" s="2"/>
-      <c r="C217" s="3"/>
-      <c r="D217" s="3"/>
-      <c r="E217" s="3"/>
-      <c r="F217" s="3"/>
-      <c r="G217" s="3"/>
+      <c r="B217" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>841</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>836</v>
+      </c>
+      <c r="E217" s="3" t="s">
+        <v>831</v>
+      </c>
+      <c r="F217" s="3" t="s">
+        <v>840</v>
+      </c>
+      <c r="G217" s="3" t="s">
+        <v>536</v>
+      </c>
       <c r="H217" s="9"/>
     </row>
-    <row r="218" spans="1:8">
+    <row r="218" spans="1:8" ht="55.2">
       <c r="A218" s="1">
         <v>217</v>
       </c>
-      <c r="B218" s="2"/>
-      <c r="C218" s="3"/>
-      <c r="D218" s="3"/>
-      <c r="E218" s="3"/>
-      <c r="F218" s="3"/>
+      <c r="B218" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>842</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>837</v>
+      </c>
+      <c r="E218" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="F218" s="3" t="s">
+        <v>839</v>
+      </c>
       <c r="G218" s="3"/>
       <c r="H218" s="9"/>
     </row>
-    <row r="219" spans="1:8">
+    <row r="219" spans="1:8" ht="69">
       <c r="A219" s="1">
         <v>218</v>
       </c>
-      <c r="B219" s="2"/>
-      <c r="C219" s="3"/>
-      <c r="D219" s="3"/>
-      <c r="E219" s="3"/>
-      <c r="F219" s="3"/>
-      <c r="G219" s="3"/>
+      <c r="B219" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="E219" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="F219" s="3" t="s">
+        <v>838</v>
+      </c>
+      <c r="G219" s="3" t="s">
+        <v>536</v>
+      </c>
       <c r="H219" s="9"/>
     </row>
     <row r="220" spans="1:8">

--- a/yougo.xlsx
+++ b/yougo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\Beat Saber\MAIN\GitHub\bs-jpmapping-glossary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41704D08-1813-408A-A011-BD7C96CF007B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC4E82F3-7AA4-4F18-BED9-8028B6BB3B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9540" yWindow="4860" windowWidth="24972" windowHeight="19140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2220" yWindow="1080" windowWidth="26088" windowHeight="22092" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="公開用データ" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1127" uniqueCount="844">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2299" uniqueCount="859">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -5866,18 +5866,6 @@
     </rPh>
     <rPh sb="66" eb="67">
       <t>ヨ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>譜面のノーツ間隔から算出される、「実質的なスイング速度」。
-曲のBPMが同じでも、要求される腕の振りの速さはノーツ配置によって異なる為、それをわかりやすく示す為のBeat Saber固有の指標である。effective BPMの略。
-片手でダウン・アップと連続で切る配置において、ノーツ間隔が「1/2ビート」の時、スイング速度eBPMは「その曲のBPM」と一致し、これが基準（等倍）となる。
-・1/4ビート間隔の場合：eBPMは2倍（スイングは倍の速さ）
-・1/1ビート間隔の場合：eBPMは半分（スイングはゆっくり）
-ざっくり言えば、120BPMの曲で1/4間隔のノーツを置いた場合、それは240BPMの曲の難しさとイコールになるという考え方である。</t>
-    <rPh sb="51" eb="52">
-      <t>ハヤ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -7296,70 +7284,6 @@
   </si>
   <si>
     <t>サイバーラーメン</t>
-  </si>
-  <si>
-    <t>AssetBundleを譜面で使用可能にするMod。マッパーは各種アセット（3Dモデル、画像、ポストプロセス・シェーダー等）を用意し、譜面の中で使用できる。
-Chroma、NoodleExtensionsに並ぶ、譜面の拡張Mod。</t>
-    <rPh sb="12" eb="14">
-      <t>フメン</t>
-    </rPh>
-    <rPh sb="15" eb="19">
-      <t>シヨウカノウ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>カクシュ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>ガゾウ</t>
-    </rPh>
-    <rPh sb="60" eb="61">
-      <t>トウ</t>
-    </rPh>
-    <rPh sb="63" eb="65">
-      <t>ヨウイ</t>
-    </rPh>
-    <rPh sb="67" eb="69">
-      <t>フメン</t>
-    </rPh>
-    <rPh sb="70" eb="71">
-      <t>ナカ</t>
-    </rPh>
-    <rPh sb="72" eb="74">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="103" eb="104">
-      <t>ナラ</t>
-    </rPh>
-    <rPh sb="106" eb="108">
-      <t>フメン</t>
-    </rPh>
-    <rPh sb="109" eb="111">
-      <t>カクチョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ノーツがスポーンしてからプレイヤーの元に到達するまでのビート数(拍数)。ノーツの表示タイミングを決める譜面の設定値。Half-Jump-Durationの略。
-関連: JD、リアクションタイム、HJDライン</t>
-    <rPh sb="32" eb="34">
-      <t>ハクスウ</t>
-    </rPh>
-    <rPh sb="48" eb="49">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>フメン</t>
-    </rPh>
-    <rPh sb="54" eb="57">
-      <t>セッテイチ</t>
-    </rPh>
-    <rPh sb="77" eb="78">
-      <t>リャク</t>
-    </rPh>
-    <rPh sb="80" eb="82">
-      <t>カンレン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>ChroMapperや公式エディタにおいて、HJDの位置に表示される赤いラインのこと。
@@ -8415,44 +8339,6 @@
     </rPh>
     <rPh sb="144" eb="146">
       <t>トウトウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>標準的な難易度単位を指した言葉。EasyからExpertPlusまでの5段階がある。英語ではDifficulty。略してdiff。
-Standard区分で5難易度揃っていることをフルスプレッドと呼ぶ。</t>
-    <rPh sb="0" eb="3">
-      <t>ヒョウジュンテキ</t>
-    </rPh>
-    <rPh sb="4" eb="7">
-      <t>ナンイド</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>タンイ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>サ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>コトバ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>エイゴ</t>
-    </rPh>
-    <rPh sb="57" eb="58">
-      <t>リャク</t>
-    </rPh>
-    <rPh sb="74" eb="76">
-      <t>クブン</t>
-    </rPh>
-    <rPh sb="78" eb="81">
-      <t>ナンイド</t>
-    </rPh>
-    <rPh sb="81" eb="82">
-      <t>ソロ</t>
-    </rPh>
-    <rPh sb="97" eb="98">
-      <t>ヨ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -9179,51 +9065,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>譜面データから生成される、その譜面を識別する為の40桁の英数字（16進数）のこと。
-一意の値であり、譜面に少しでも変更を加えると異なる値になる。ゲーム側やScoreSaber、BeatLeaderなどは、譜面ハッシュを元に記録を管理している為、リパブリッシュの際にはリーダーボードも新しいまっさらな状態になる。
-※リパブリッシュで過去のリーダーボードが消えるわけではなく、譜面のバージョン（譜面ハッシュ）ごとにリーダーボードが生成・管理される仕組み。BeatLeaderではリーダーボードページから過去バージョンのリーダーボードを簡単に確認できる</t>
-    <rPh sb="111" eb="113">
-      <t>キロク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>maphash</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>EasyからExpertPlusまで、標準的なすべての[[難易度|難易度（Difficulty）]]が網羅されていること。およびその譜面。
-Standard区分での難易度が揃っていることが本質であり、例えばコラボ等でEx+が2つありEasyが欠けている5難易度展開はフルスプレッドとはならない。</t>
-    <rPh sb="29" eb="32">
-      <t>ナンイド</t>
-    </rPh>
-    <rPh sb="78" eb="80">
-      <t>クブン</t>
-    </rPh>
-    <rPh sb="82" eb="85">
-      <t>ナンイド</t>
-    </rPh>
-    <rPh sb="86" eb="87">
-      <t>ソロ</t>
-    </rPh>
-    <rPh sb="94" eb="96">
-      <t>ホンシツ</t>
-    </rPh>
-    <rPh sb="100" eb="101">
-      <t>タト</t>
-    </rPh>
-    <rPh sb="106" eb="107">
-      <t>トウ</t>
-    </rPh>
-    <rPh sb="121" eb="122">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="127" eb="130">
-      <t>ナンイド</t>
-    </rPh>
-    <rPh sb="130" eb="132">
-      <t>テンカイ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -9975,6 +9817,440 @@
     </rPh>
     <rPh sb="181" eb="183">
       <t>サマザマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UnityのAssetBundleを譜面で使用可能にするMod。マッパーは各種アセット（3Dモデル、画像、ポストプロセス・シェーダー等）を用意し、譜面の中で使用できる。
+Chroma、NoodleExtensionsに並ぶ、譜面の拡張Mod。</t>
+    <rPh sb="18" eb="20">
+      <t>フメン</t>
+    </rPh>
+    <rPh sb="21" eb="25">
+      <t>シヨウカノウ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>カクシュ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="66" eb="67">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>ヨウイ</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>フメン</t>
+    </rPh>
+    <rPh sb="76" eb="77">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="109" eb="110">
+      <t>ナラ</t>
+    </rPh>
+    <rPh sb="112" eb="114">
+      <t>フメン</t>
+    </rPh>
+    <rPh sb="115" eb="117">
+      <t>カクチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ノーツがスポーンしてからプレイヤーの元に到達するまでのビート数(拍数)。ノーツの表示タイミングを決める譜面の設定値。Half-Jump-Duration（ハーフジャンプデュレーション）の略。
+関連: JD、リアクションタイム、HJDライン</t>
+    <rPh sb="32" eb="34">
+      <t>ハクスウ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>フメン</t>
+    </rPh>
+    <rPh sb="54" eb="57">
+      <t>セッテイチ</t>
+    </rPh>
+    <rPh sb="93" eb="94">
+      <t>リャク</t>
+    </rPh>
+    <rPh sb="96" eb="98">
+      <t>カンレン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>譜面のノーツ間隔から算出される、「実質的なスイング速度」。
+曲のBPMが同じでも、要求される腕の振りの速さはノーツ配置によって異なる為、それをわかりやすく示す為のBeat Saber固有の指標である。effective BPMの略。
+片手でダウン・アップと連続で切る配置において、ノーツ間隔が「1/2ビート」の時、スイング速度eBPMは「その曲のBPM」と一致し、これが基準（等倍）となる。
+・1/4ビート間隔の場合：eBPMは2倍（スイングは倍の速さ）
+・1/1ビート間隔の場合：eBPMは半分（スイングはゆっくり）
+ざっくり言えば、120BPMの曲で片手1/4間隔のノーツを置いた場合、それは240BPMの曲の難しさとイコール（eBPM240）になるという考え方である。</t>
+    <rPh sb="51" eb="52">
+      <t>ハヤ</t>
+    </rPh>
+    <rPh sb="277" eb="279">
+      <t>カタテ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>譜面データから生成される、その譜面を識別する為の40桁の英数字（16進数）のこと。
+一意の値であり、譜面に少しでも変更を加えると異なる値になる。ゲーム側やScoreSaber、BeatLeaderなどは、譜面ハッシュを元に記録を管理している為、リパブリッシュによってハッシュが変わるとリーダーボードも新しいまっさらな状態になる。
+※リパブリッシュで過去のリーダーボードが消えるわけではなく、譜面のバージョン（譜面ハッシュ）ごとにリーダーボードが生成・管理される仕組み。BeatLeaderではリーダーボードページから過去バージョンのリーダーボードを簡単に確認できる</t>
+    <rPh sb="111" eb="113">
+      <t>キロク</t>
+    </rPh>
+    <rPh sb="138" eb="139">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>難易度単位を指した言葉。EasyからExpertPlusまでの5段階がある。英語ではDifficulty。略してdiff。
+Standard区分で5難易度揃っていることをフルスプレッドと呼ぶ。</t>
+    <rPh sb="0" eb="3">
+      <t>ナンイド</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>タンイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コトバ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>エイゴ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>リャク</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>クブン</t>
+    </rPh>
+    <rPh sb="74" eb="77">
+      <t>ナンイド</t>
+    </rPh>
+    <rPh sb="77" eb="78">
+      <t>ソロ</t>
+    </rPh>
+    <rPh sb="93" eb="94">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EasyからExpertPlusまで、標準的な５つの[[難易度|難易度（Difficulty）]]が網羅されていること。およびその譜面。
+Standard区分での難易度が揃っていることが本質であり、例えばコラボ等でEx+が2つありEasyが欠けている5難易度展開はフルスプレッドとはならない。</t>
+    <rPh sb="28" eb="31">
+      <t>ナンイド</t>
+    </rPh>
+    <rPh sb="77" eb="79">
+      <t>クブン</t>
+    </rPh>
+    <rPh sb="81" eb="84">
+      <t>ナンイド</t>
+    </rPh>
+    <rPh sb="85" eb="86">
+      <t>ソロ</t>
+    </rPh>
+    <rPh sb="93" eb="95">
+      <t>ホンシツ</t>
+    </rPh>
+    <rPh sb="99" eb="100">
+      <t>タト</t>
+    </rPh>
+    <rPh sb="105" eb="106">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="120" eb="121">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="126" eb="129">
+      <t>ナンイド</t>
+    </rPh>
+    <rPh sb="129" eb="131">
+      <t>テンカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アンランク</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Group Lighting System</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダウンマッピング</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Modder</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>rankable</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ランカブル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ランク譜面ではない譜面のこと。
+BeatSaverに公開されている譜面のほとんどはアンランク譜面である。</t>
+    <rPh sb="3" eb="5">
+      <t>フメン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>フメン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>コウカイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>フメン</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>フメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>unrank</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>グループライティングシステム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Downmapping</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モッダー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ライトイベントを「グループ」で管理・制御できるV3ライティング特有のシステム。
+「グループイベント」という箱を設置し、その中に各種ライトイベントやアニメーションイベントを好きなだけ配置できる。これにより詳細な制御が可能となった。
+V3ライティングシステムの別名（公式名称）。略してGLS。BeatLeaderではV3ライトの譜面には「GLS」のタグが付く。</t>
+    <rPh sb="53" eb="54">
+      <t>ハコ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>カクシュ</t>
+    </rPh>
+    <rPh sb="85" eb="86">
+      <t>ス</t>
+    </rPh>
+    <rPh sb="90" eb="92">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="101" eb="103">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="104" eb="106">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="107" eb="109">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="128" eb="130">
+      <t>ベツメイ</t>
+    </rPh>
+    <rPh sb="131" eb="133">
+      <t>コウシキ</t>
+    </rPh>
+    <rPh sb="133" eb="135">
+      <t>メイショウ</t>
+    </rPh>
+    <rPh sb="137" eb="138">
+      <t>リャク</t>
+    </rPh>
+    <rPh sb="162" eb="164">
+      <t>フメン</t>
+    </rPh>
+    <rPh sb="175" eb="176">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>難易度を落としてマッピングすること。主に、Expert+などを作成した後、それより下の難易度を作成することを指す。
+意図的に難易度を落とし、特定のプレイヤーレベルを想定してマッピングを行わなければならない為、Expert+とはまた違ったダウンマッピング特有の考え方が必要となる。
+また、Expert+単体であっても、曲の音数を間引きながら難易度を落としてマッピングする行為はダウンマッピングと解釈できる。
+ダウンマップとも。</t>
+    <rPh sb="58" eb="61">
+      <t>イトテキ</t>
+    </rPh>
+    <rPh sb="62" eb="65">
+      <t>ナンイド</t>
+    </rPh>
+    <rPh sb="66" eb="67">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="82" eb="84">
+      <t>ソウテイ</t>
+    </rPh>
+    <rPh sb="92" eb="93">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="102" eb="103">
+      <t>タメ</t>
+    </rPh>
+    <rPh sb="115" eb="116">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="126" eb="128">
+      <t>トクユウ</t>
+    </rPh>
+    <rPh sb="129" eb="130">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="131" eb="132">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="133" eb="135">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="150" eb="152">
+      <t>タンタイ</t>
+    </rPh>
+    <rPh sb="184" eb="186">
+      <t>コウイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>直訳で「ランク可能」。ScoreSaberやBeatLeaderなどのランク用マッピングの文脈で、特定の配置や譜面を指して「ランク化できる（許される）」ことを表す言葉。
+主に、ランク基準ギリギリな配置や、賛否がわかれそうな配置に対して、「これはrankable？」「それはrankableだ」みたいな例で用いられる。
+rankableではない場合は「not rankable」「unrankable」</t>
+    <rPh sb="0" eb="2">
+      <t>チョクヤク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>フメン</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>ユル</t>
+    </rPh>
+    <rPh sb="79" eb="80">
+      <t>アラワ</t>
+    </rPh>
+    <rPh sb="81" eb="83">
+      <t>コトバ</t>
+    </rPh>
+    <rPh sb="85" eb="86">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="91" eb="93">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="98" eb="100">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="102" eb="104">
+      <t>サンピ</t>
+    </rPh>
+    <rPh sb="111" eb="113">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="114" eb="115">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="150" eb="151">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="152" eb="153">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="171" eb="173">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ランク譜面において、ランク化の必須プロセスである[[Modding]]を行う役職の人のこと。各ランクチームには複数人のModderが在籍している。
+JBSLにおいても、JBSL用の譜面を応募する際にはJBSLチームのModderがModdingを行ってくれる。</t>
+    <rPh sb="3" eb="5">
+      <t>フメン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ヤクショク</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="55" eb="58">
+      <t>フクスウニン</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>ザイセキ</t>
+    </rPh>
+    <rPh sb="88" eb="89">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="90" eb="92">
+      <t>フメン</t>
+    </rPh>
+    <rPh sb="93" eb="95">
+      <t>オウボ</t>
+    </rPh>
+    <rPh sb="97" eb="98">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="123" eb="124">
+      <t>オコナ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -10490,7 +10766,7 @@
         <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>382</v>
@@ -10535,7 +10811,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>384</v>
@@ -10584,7 +10860,7 @@
         <v>248</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="7" t="s">
@@ -10608,7 +10884,7 @@
         <v>255</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="7" t="s">
@@ -10669,7 +10945,7 @@
         <v>20</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>21</v>
@@ -10755,7 +11031,7 @@
         <v>27</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>390</v>
@@ -10779,7 +11055,7 @@
         <v>29</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>391</v>
@@ -10823,7 +11099,7 @@
         <v>32</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>33</v>
@@ -10843,7 +11119,7 @@
         <v>34</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>703</v>
+        <v>840</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>35</v>
@@ -10865,7 +11141,7 @@
         <v>36</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>37</v>
@@ -11001,7 +11277,7 @@
         <v>46</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>319</v>
@@ -11025,7 +11301,7 @@
         <v>48</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>393</v>
@@ -11219,7 +11495,7 @@
         <v>58</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>59</v>
@@ -11265,10 +11541,10 @@
         <v>62</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>266</v>
@@ -11313,7 +11589,7 @@
         <v>64</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>759</v>
+        <v>839</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>65</v>
@@ -11335,7 +11611,7 @@
         <v>66</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>404</v>
@@ -11559,7 +11835,7 @@
         <v>80</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>81</v>
@@ -11671,7 +11947,7 @@
         <v>541</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>88</v>
@@ -11693,7 +11969,7 @@
         <v>89</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>90</v>
@@ -11715,7 +11991,7 @@
         <v>91</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>416</v>
@@ -11737,7 +12013,7 @@
         <v>542</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>625</v>
@@ -11759,7 +12035,7 @@
         <v>546</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>92</v>
@@ -11778,10 +12054,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>93</v>
@@ -11800,10 +12076,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>94</v>
@@ -11847,7 +12123,7 @@
         <v>96</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>97</v>
@@ -11867,7 +12143,7 @@
         <v>98</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>99</v>
@@ -11999,7 +12275,7 @@
         <v>109</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>421</v>
@@ -12023,7 +12299,7 @@
         <v>110</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>422</v>
@@ -12135,7 +12411,7 @@
         <v>116</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>328</v>
@@ -12157,7 +12433,7 @@
         <v>117</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>427</v>
@@ -12223,7 +12499,7 @@
         <v>122</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>428</v>
@@ -12245,7 +12521,7 @@
         <v>123</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>429</v>
@@ -12311,7 +12587,7 @@
         <v>128</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>432</v>
@@ -12447,7 +12723,7 @@
         <v>135</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>437</v>
@@ -12493,7 +12769,7 @@
         <v>138</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>439</v>
@@ -12539,7 +12815,7 @@
         <v>140</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>441</v>
@@ -12582,7 +12858,7 @@
         <v>590</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>300</v>
@@ -12665,7 +12941,7 @@
         <v>149</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>446</v>
@@ -12759,7 +13035,7 @@
         <v>153</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>154</v>
@@ -12843,7 +13119,7 @@
         <v>160</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>452</v>
@@ -12865,7 +13141,7 @@
         <v>161</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>453</v>
@@ -12887,7 +13163,7 @@
         <v>162</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>454</v>
@@ -12909,7 +13185,7 @@
         <v>163</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="D113" s="3" t="s">
         <v>455</v>
@@ -13107,7 +13383,7 @@
         <v>176</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="D122" s="3" t="s">
         <v>177</v>
@@ -13153,7 +13429,7 @@
         <v>180</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>458</v>
@@ -13221,7 +13497,7 @@
         <v>183</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>828</v>
+        <v>822</v>
       </c>
       <c r="D127" s="3" t="s">
         <v>461</v>
@@ -13265,7 +13541,7 @@
         <v>186</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="D129" s="3" t="s">
         <v>463</v>
@@ -13287,7 +13563,7 @@
         <v>187</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="D130" s="3" t="s">
         <v>624</v>
@@ -13307,7 +13583,7 @@
         <v>188</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="D131" s="3" t="s">
         <v>464</v>
@@ -13349,7 +13625,7 @@
         <v>191</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="D133" s="3" t="s">
         <v>466</v>
@@ -13369,7 +13645,7 @@
         <v>192</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="D134" s="3" t="s">
         <v>345</v>
@@ -13410,16 +13686,16 @@
         <v>135</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="F136" s="3"/>
       <c r="G136" s="3" t="s">
@@ -13435,7 +13711,7 @@
         <v>193</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="D137" s="3" t="s">
         <v>467</v>
@@ -13459,7 +13735,7 @@
         <v>194</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="D138" s="3" t="s">
         <v>468</v>
@@ -13481,7 +13757,7 @@
         <v>195</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="D139" s="3" t="s">
         <v>346</v>
@@ -13571,7 +13847,7 @@
         <v>200</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D143" s="3" t="s">
         <v>347</v>
@@ -13593,7 +13869,7 @@
         <v>201</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D144" s="3" t="s">
         <v>472</v>
@@ -13637,7 +13913,7 @@
         <v>203</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D146" s="3" t="s">
         <v>474</v>
@@ -13659,7 +13935,7 @@
         <v>204</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="D147" s="3" t="s">
         <v>475</v>
@@ -13703,7 +13979,7 @@
         <v>206</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="D149" s="3" t="s">
         <v>349</v>
@@ -13763,7 +14039,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="41.4">
+    <row r="152" spans="1:8" ht="27.6">
       <c r="A152" s="1">
         <v>151</v>
       </c>
@@ -13771,7 +14047,7 @@
         <v>479</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>793</v>
+        <v>842</v>
       </c>
       <c r="D152" s="3" t="s">
         <v>478</v>
@@ -13813,7 +14089,7 @@
         <v>210</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>818</v>
+        <v>843</v>
       </c>
       <c r="D154" s="3" t="s">
         <v>480</v>
@@ -13857,7 +14133,7 @@
         <v>212</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="D156" s="3" t="s">
         <v>482</v>
@@ -13969,7 +14245,7 @@
         <v>219</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="D161" s="3" t="s">
         <v>486</v>
@@ -13982,7 +14258,7 @@
         <v>536</v>
       </c>
       <c r="H161" s="9" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="41.4">
@@ -14017,7 +14293,7 @@
         <v>220</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D163" s="3" t="s">
         <v>358</v>
@@ -14061,7 +14337,7 @@
         <v>223</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D165" s="3" t="s">
         <v>360</v>
@@ -14129,10 +14405,10 @@
         <v>226</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E168" s="3" t="s">
         <v>226</v>
@@ -14148,10 +14424,10 @@
         <v>168</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="D169" s="3" t="s">
         <v>397</v>
@@ -14162,7 +14438,7 @@
       <c r="F169" s="3"/>
       <c r="G169" s="3"/>
       <c r="H169" s="8" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="124.2">
@@ -14173,7 +14449,7 @@
         <v>363</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D170" s="3" t="s">
         <v>488</v>
@@ -14241,7 +14517,7 @@
         <v>229</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="D173" s="3" t="s">
         <v>43</v>
@@ -14282,7 +14558,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C175" s="3" t="s">
         <v>574</v>
@@ -14307,7 +14583,7 @@
         <v>231</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="D176" s="3" t="s">
         <v>492</v>
@@ -14329,7 +14605,7 @@
         <v>232</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="D177" s="3" t="s">
         <v>493</v>
@@ -14351,7 +14627,7 @@
         <v>233</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="D178" s="3" t="s">
         <v>495</v>
@@ -14393,7 +14669,7 @@
         <v>235</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="D180" s="3" t="s">
         <v>496</v>
@@ -14415,7 +14691,7 @@
         <v>236</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="D181" s="3" t="s">
         <v>497</v>
@@ -14434,10 +14710,10 @@
         <v>181</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="D182" s="3" t="s">
         <v>370</v>
@@ -14456,10 +14732,10 @@
         <v>182</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="D183" s="3" t="s">
         <v>371</v>
@@ -14569,7 +14845,7 @@
         <v>242</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D188" s="3" t="s">
         <v>376</v>
@@ -14615,7 +14891,7 @@
         <v>243</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D190" s="3" t="s">
         <v>378</v>
@@ -14659,7 +14935,7 @@
         <v>532</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>758</v>
+        <v>838</v>
       </c>
       <c r="D192" s="3" t="s">
         <v>556</v>
@@ -14681,7 +14957,7 @@
         <v>688</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="D193" s="3" t="s">
         <v>558</v>
@@ -14725,7 +15001,7 @@
         <v>608</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="D195" s="3" t="s">
         <v>610</v>
@@ -14789,10 +15065,10 @@
         <v>646</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="E198" s="3" t="s">
         <v>647</v>
@@ -14813,7 +15089,7 @@
         <v>648</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="D199" s="3" t="s">
         <v>662</v>
@@ -14835,7 +15111,7 @@
         <v>649</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="D200" s="3" t="s">
         <v>663</v>
@@ -14927,7 +15203,7 @@
         <v>653</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D204" s="3" t="s">
         <v>667</v>
@@ -14968,16 +15244,16 @@
         <v>205</v>
       </c>
       <c r="B206" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="D206" s="3" t="s">
         <v>731</v>
       </c>
-      <c r="C206" s="3" t="s">
-        <v>743</v>
-      </c>
-      <c r="D206" s="3" t="s">
-        <v>732</v>
-      </c>
       <c r="E206" s="3" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="F206" s="3"/>
       <c r="G206" s="3" t="s">
@@ -14993,7 +15269,7 @@
         <v>654</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>816</v>
+        <v>841</v>
       </c>
       <c r="D207" s="3" t="s">
         <v>668</v>
@@ -15002,7 +15278,7 @@
         <v>669</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="G207" s="3" t="s">
         <v>536</v>
@@ -15026,7 +15302,7 @@
         <v>655</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="G208" s="3" t="s">
         <v>536</v>
@@ -15041,7 +15317,7 @@
         <v>658</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="D209" s="3" t="s">
         <v>672</v>
@@ -15054,7 +15330,7 @@
         <v>536</v>
       </c>
       <c r="H209" s="8" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
     </row>
     <row r="210" spans="1:8" ht="27.6">
@@ -15085,7 +15361,7 @@
         <v>660</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D211" s="3" t="s">
         <v>675</v>
@@ -15094,7 +15370,7 @@
         <v>660</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="G211" s="3" t="s">
         <v>536</v>
@@ -15109,7 +15385,7 @@
         <v>661</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="D212" s="3" t="s">
         <v>676</v>
@@ -15131,7 +15407,7 @@
         <v>692</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="D213" s="3" t="s">
         <v>694</v>
@@ -15153,7 +15429,7 @@
         <v>693</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="D214" s="3" t="s">
         <v>695</v>
@@ -15172,23 +15448,23 @@
         <v>214</v>
       </c>
       <c r="B215" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="D215" s="3" t="s">
         <v>715</v>
       </c>
-      <c r="C215" s="3" t="s">
-        <v>718</v>
-      </c>
-      <c r="D215" s="3" t="s">
-        <v>716</v>
-      </c>
       <c r="E215" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F215" s="3"/>
       <c r="G215" s="3" t="s">
         <v>536</v>
       </c>
       <c r="H215" s="8" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="216" spans="1:8" ht="124.2">
@@ -15196,25 +15472,25 @@
         <v>215</v>
       </c>
       <c r="B216" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="C216" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>735</v>
+      </c>
+      <c r="E216" s="3" t="s">
         <v>734</v>
       </c>
-      <c r="C216" s="3" t="s">
-        <v>760</v>
-      </c>
-      <c r="D216" s="3" t="s">
+      <c r="F216" s="3" t="s">
+        <v>737</v>
+      </c>
+      <c r="G216" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="H216" s="8" t="s">
         <v>736</v>
-      </c>
-      <c r="E216" s="3" t="s">
-        <v>735</v>
-      </c>
-      <c r="F216" s="3" t="s">
-        <v>738</v>
-      </c>
-      <c r="G216" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="H216" s="8" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="217" spans="1:8" ht="41.4">
@@ -15222,19 +15498,19 @@
         <v>216</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="F217" s="3" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="G217" s="3" t="s">
         <v>536</v>
@@ -15246,19 +15522,19 @@
         <v>217</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>837</v>
+        <v>831</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="F218" s="3" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="G218" s="3"/>
       <c r="H218" s="9"/>
@@ -15268,83 +15544,133 @@
         <v>218</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="G219" s="3" t="s">
         <v>536</v>
       </c>
       <c r="H219" s="9"/>
     </row>
-    <row r="220" spans="1:8">
+    <row r="220" spans="1:8" ht="27.6">
       <c r="A220" s="1">
         <v>219</v>
       </c>
-      <c r="B220" s="2"/>
-      <c r="C220" s="3"/>
-      <c r="D220" s="3"/>
-      <c r="E220" s="3"/>
+      <c r="B220" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="E220" s="3" t="s">
+        <v>844</v>
+      </c>
       <c r="F220" s="3"/>
-      <c r="G220" s="3"/>
+      <c r="G220" s="3" t="s">
+        <v>536</v>
+      </c>
       <c r="H220" s="9"/>
     </row>
-    <row r="221" spans="1:8">
+    <row r="221" spans="1:8" ht="69">
       <c r="A221" s="1">
         <v>220</v>
       </c>
-      <c r="B221" s="2"/>
-      <c r="C221" s="3"/>
-      <c r="D221" s="3"/>
-      <c r="E221" s="3"/>
+      <c r="B221" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="C221" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>852</v>
+      </c>
+      <c r="E221" s="3" t="s">
+        <v>852</v>
+      </c>
       <c r="F221" s="3"/>
-      <c r="G221" s="3"/>
+      <c r="G221" s="3" t="s">
+        <v>536</v>
+      </c>
       <c r="H221" s="9"/>
     </row>
-    <row r="222" spans="1:8">
+    <row r="222" spans="1:8" ht="96.6">
       <c r="A222" s="1">
         <v>221</v>
       </c>
-      <c r="B222" s="2"/>
-      <c r="C222" s="3"/>
-      <c r="D222" s="3"/>
-      <c r="E222" s="3"/>
+      <c r="B222" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="C222" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>853</v>
+      </c>
+      <c r="E222" s="3" t="s">
+        <v>846</v>
+      </c>
       <c r="F222" s="3"/>
-      <c r="G222" s="3"/>
+      <c r="G222" s="3" t="s">
+        <v>536</v>
+      </c>
       <c r="H222" s="9"/>
     </row>
-    <row r="223" spans="1:8">
+    <row r="223" spans="1:8" ht="41.4">
       <c r="A223" s="1">
         <v>222</v>
       </c>
-      <c r="B223" s="2"/>
-      <c r="C223" s="3"/>
-      <c r="D223" s="3"/>
-      <c r="E223" s="3"/>
+      <c r="B223" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>858</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>854</v>
+      </c>
+      <c r="E223" s="3" t="s">
+        <v>854</v>
+      </c>
       <c r="F223" s="3"/>
-      <c r="G223" s="3"/>
+      <c r="G223" s="3" t="s">
+        <v>536</v>
+      </c>
       <c r="H223" s="9"/>
     </row>
-    <row r="224" spans="1:8">
+    <row r="224" spans="1:8" ht="69">
       <c r="A224" s="1">
         <v>223</v>
       </c>
-      <c r="B224" s="2"/>
-      <c r="C224" s="3"/>
-      <c r="D224" s="3"/>
-      <c r="E224" s="3"/>
+      <c r="B224" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>849</v>
+      </c>
+      <c r="E224" s="3" t="s">
+        <v>849</v>
+      </c>
       <c r="F224" s="3"/>
-      <c r="G224" s="3"/>
+      <c r="G224" s="3" t="s">
+        <v>536</v>
+      </c>
       <c r="H224" s="9"/>
     </row>
     <row r="225" spans="1:8">
@@ -15507,27 +15833,27 @@
   <sheetData>
     <row r="2" spans="2:2">
       <c r="B2" s="10" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
     </row>
     <row r="3" spans="2:2">
       <c r="B3" s="10" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" s="10" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" s="10" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
     </row>
     <row r="6" spans="2:2">
       <c r="B6" s="10" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
     </row>
   </sheetData>

--- a/yougo.xlsx
+++ b/yougo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\Beat Saber\MAIN\GitHub\bs-jpmapping-glossary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC4E82F3-7AA4-4F18-BED9-8028B6BB3B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC8F6D7-EDD9-4E0D-9176-BAE2EDF56C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2220" yWindow="1080" windowWidth="26088" windowHeight="22092" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8280" yWindow="5028" windowWidth="26088" windowHeight="22092" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="公開用データ" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2299" uniqueCount="859">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="859">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -10208,48 +10208,58 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ランク譜面において、ランク化の必須プロセスである[[Modding]]を行う役職の人のこと。各ランクチームには複数人のModderが在籍している。
+    <t>① ゲーム用のModを作成する人のこと。
+② ランク譜面において、ランク化の必須プロセスである[[Modding]]を行う役職の人のこと。各ランクチームには複数人のModderが在籍している。
 JBSLにおいても、JBSL用の譜面を応募する際にはJBSLチームのModderがModdingを行ってくれる。</t>
-    <rPh sb="3" eb="5">
+    <rPh sb="5" eb="6">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="26" eb="28">
       <t>フメン</t>
     </rPh>
-    <rPh sb="13" eb="14">
+    <rPh sb="36" eb="37">
       <t>カ</t>
     </rPh>
-    <rPh sb="15" eb="17">
+    <rPh sb="38" eb="40">
       <t>ヒッス</t>
     </rPh>
-    <rPh sb="36" eb="37">
+    <rPh sb="59" eb="60">
       <t>オコナ</t>
     </rPh>
-    <rPh sb="38" eb="40">
+    <rPh sb="61" eb="63">
       <t>ヤクショク</t>
     </rPh>
-    <rPh sb="41" eb="42">
+    <rPh sb="64" eb="65">
       <t>ヒト</t>
     </rPh>
-    <rPh sb="46" eb="47">
+    <rPh sb="69" eb="70">
       <t>カク</t>
     </rPh>
-    <rPh sb="55" eb="58">
+    <rPh sb="78" eb="81">
       <t>フクスウニン</t>
     </rPh>
-    <rPh sb="66" eb="68">
+    <rPh sb="89" eb="91">
       <t>ザイセキ</t>
     </rPh>
-    <rPh sb="88" eb="89">
+    <rPh sb="111" eb="112">
       <t>ヨウ</t>
     </rPh>
-    <rPh sb="90" eb="92">
+    <rPh sb="113" eb="115">
       <t>フメン</t>
     </rPh>
-    <rPh sb="93" eb="95">
+    <rPh sb="116" eb="118">
       <t>オウボ</t>
     </rPh>
-    <rPh sb="97" eb="98">
+    <rPh sb="120" eb="121">
       <t>サイ</t>
     </rPh>
-    <rPh sb="123" eb="124">
+    <rPh sb="146" eb="147">
       <t>オコナ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -15629,7 +15639,7 @@
       </c>
       <c r="H222" s="9"/>
     </row>
-    <row r="223" spans="1:8" ht="41.4">
+    <row r="223" spans="1:8" ht="55.2">
       <c r="A223" s="1">
         <v>222</v>
       </c>

--- a/yougo.xlsx
+++ b/yougo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\Beat Saber\MAIN\GitHub\bs-jpmapping-glossary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC8F6D7-EDD9-4E0D-9176-BAE2EDF56C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D0553A-52CB-4125-A6C9-49E239C6E298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8280" yWindow="5028" windowWidth="26088" windowHeight="22092" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2076" yWindow="984" windowWidth="26088" windowHeight="22092" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="公開用データ" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="859">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="863">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -1672,56 +1672,6 @@
     <t>ハイパーウォール</t>
   </si>
   <si>
-    <t>壁の持続時間（奥行き）を負の値にした壁。通常の壁よりも高速で流れる。
-ゲームの想定されてない挙動である為、基本的には推奨されない。</t>
-    <rPh sb="0" eb="1">
-      <t>カベ</t>
-    </rPh>
-    <rPh sb="2" eb="6">
-      <t>ジゾクジカン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>オクユ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>フ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>アタイ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>カベ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ツウジョウ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>カベ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>コウソク</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>ナガ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>ソウテイ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>キョドウ</t>
-    </rPh>
-    <rPh sb="51" eb="52">
-      <t>タメ</t>
-    </rPh>
-    <rPh sb="53" eb="56">
-      <t>キホンテキ</t>
-    </rPh>
-    <rPh sb="58" eb="60">
-      <t>スイショウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>オートライト</t>
   </si>
   <si>
@@ -3004,9 +2954,6 @@
       <t>キロク</t>
     </rPh>
     <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>NoodleExtensionsを利用し、実際には切れない（判定がない）視覚的な演出として配置されるノーツ。</t>
   </si>
   <si>
     <t>NoodleExtensions</t>
@@ -4157,58 +4104,6 @@
 手首、腕、肩などの可動域を積極的に使い、「どう切るか」という技術的な読み・アプローチの難しさに特化している。</t>
     <rPh sb="43" eb="46">
       <t>セッキョクテキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>同じ色・同じ方向のノーツが、横に2つ以上並んでいる配置。通常のスイングでは取りこぼしてしまう為、ヒットボックスや方向判定の仕組みを利用（悪用）した切り方が求められる。特殊な配置。ロロッペノーツとも。</t>
-    <rPh sb="2" eb="3">
-      <t>イロ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>オナ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ハイチ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>ツウジョウ</t>
-    </rPh>
-    <rPh sb="37" eb="38">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="46" eb="47">
-      <t>タメ</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>ホウコウ</t>
-    </rPh>
-    <rPh sb="58" eb="60">
-      <t>ハンテイ</t>
-    </rPh>
-    <rPh sb="61" eb="63">
-      <t>シク</t>
-    </rPh>
-    <rPh sb="65" eb="67">
-      <t>リヨウ</t>
-    </rPh>
-    <rPh sb="68" eb="70">
-      <t>アクヨウ</t>
-    </rPh>
-    <rPh sb="73" eb="74">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="75" eb="76">
-      <t>カタ</t>
-    </rPh>
-    <rPh sb="77" eb="78">
-      <t>モト</t>
-    </rPh>
-    <rPh sb="83" eb="85">
-      <t>トクシュ</t>
-    </rPh>
-    <rPh sb="86" eb="88">
-      <t>ハイチ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4905,15 +4800,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>プレイヤーの顔面に向かって飛んでくる中央2マスいずれかのノーツのこと。プレイヤーの視界を覆ってしまう為、ビジョンブロックの問題を招きやすい。慣れないうちは置かないほうがいいマス。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>NoodleExtensionsを利用し、触れてもダメージを受けない演出用の壁。
-バニラでも壁の幅を負の値にすることで同様の壁を置くことができるが、本来想定されていない動作である為あまり推奨されない。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ノーツが出現してからプレイヤーに到達するまでの物理的な距離。Unity空間におけるメートル（unit）換算で、1JD=0.5m。ジャンプディスタンスの略。ジャンプ距離とも言う。
 ※正確にはJDはプレイヤーの後方にも同じだけ伸びており、1JD=1mが正しいのだが、実際の感覚では上記の考え方でよい。
 関連: リアクションタイム、HJD</t>
@@ -5478,110 +5364,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>非常に遅いスライダー。ずらし間隔が通常のスライダーより極端に遅く、ゆっくりなぞって切ることを強制させる配置である。
-ずらし間隔に明確な決まりはないが、1/8や1/4がよく見受けられる。その遅さもあって通常のスライダーとは違い、スライダーが長かったり、曲げたり、切り替えしたりといった使い方も多い。特殊な配置であり、角度点を出すことが非常に困難である為、一般的な譜面での使用はおすすめできない（アイデア次第ではあるが）。</t>
-    <rPh sb="0" eb="2">
-      <t>ヒジョウ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>オソ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ツウジョウ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>キョ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>オソ</t>
-    </rPh>
-    <rPh sb="41" eb="42">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>キョウセイ</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>ハイチ</t>
-    </rPh>
-    <rPh sb="64" eb="66">
-      <t>メイカク</t>
-    </rPh>
-    <rPh sb="67" eb="68">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="85" eb="87">
-      <t>ミウ</t>
-    </rPh>
-    <rPh sb="94" eb="95">
-      <t>オソ</t>
-    </rPh>
-    <rPh sb="100" eb="102">
-      <t>ツウジョウ</t>
-    </rPh>
-    <rPh sb="110" eb="111">
-      <t>チガ</t>
-    </rPh>
-    <rPh sb="119" eb="120">
-      <t>ナガ</t>
-    </rPh>
-    <rPh sb="125" eb="126">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="130" eb="131">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="132" eb="133">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="141" eb="142">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="143" eb="144">
-      <t>カタ</t>
-    </rPh>
-    <rPh sb="145" eb="146">
-      <t>オオ</t>
-    </rPh>
-    <rPh sb="148" eb="150">
-      <t>トクシュ</t>
-    </rPh>
-    <rPh sb="151" eb="153">
-      <t>ハイチ</t>
-    </rPh>
-    <rPh sb="157" eb="159">
-      <t>カクド</t>
-    </rPh>
-    <rPh sb="159" eb="160">
-      <t>テン</t>
-    </rPh>
-    <rPh sb="161" eb="162">
-      <t>ダ</t>
-    </rPh>
-    <rPh sb="166" eb="168">
-      <t>ヒジョウ</t>
-    </rPh>
-    <rPh sb="169" eb="171">
-      <t>コンナン</t>
-    </rPh>
-    <rPh sb="174" eb="175">
-      <t>タメ</t>
-    </rPh>
-    <rPh sb="176" eb="179">
-      <t>イッパ</t>
-    </rPh>
-    <rPh sb="180" eb="182">
-      <t>フメン</t>
-    </rPh>
-    <rPh sb="184" eb="186">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="200" eb="202">
-      <t>シダイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>プレイエリア4レーンのうち、3レーンの幅を覆う壁のこと。プレイヤーは外側レーンまで大きく避けることを余儀なくされ、転倒や家具への衝突の危険性が高い為、よほど特殊な譜面を除きこれを使用してはいけない。4レーン全てを覆う壁は4-Wide Wallであり、さらにNG。</t>
     <rPh sb="19" eb="20">
       <t>ハバ</t>
@@ -5963,38 +5745,6 @@
   </si>
   <si>
     <t>ScoreSaber</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>片手で、三角形の頂点を辿るように3つのノーツを切らせる配置パターン。
-「パリティが崩れ、リセットが発生してしまうこと」がこの配置の本質であり、DDと同様、基本的には推奨されない。※高難度テック譜面等でパリティが適切に保たれる場合はトライアングルとはならない。</t>
-    <rPh sb="0" eb="2">
-      <t>カタテ</t>
-    </rPh>
-    <rPh sb="4" eb="7">
-      <t>サンカッケイ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>チョウテン</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>タド</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>ハイチ</t>
-    </rPh>
-    <rPh sb="90" eb="93">
-      <t>コウナンド</t>
-    </rPh>
-    <rPh sb="96" eb="98">
-      <t>フメン</t>
-    </rPh>
-    <rPh sb="98" eb="99">
-      <t>トウ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -6962,40 +6712,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ノーツを同じ場所に完全に重なって配置してしまうこと。大抵はコピペミスによって起こるミスマップであり、エディター上では判別しにくい為テストプレイやマップチェッカーでの確認が大事である。</t>
-    <rPh sb="4" eb="5">
-      <t>オナ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>バショ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>カサ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>タイテイ</t>
-    </rPh>
-    <rPh sb="38" eb="39">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="55" eb="56">
-      <t>ジョウ</t>
-    </rPh>
-    <rPh sb="58" eb="60">
-      <t>ハンベツ</t>
-    </rPh>
-    <rPh sb="64" eb="65">
-      <t>タメ</t>
-    </rPh>
-    <rPh sb="82" eb="84">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="85" eb="87">
-      <t>ダイジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ノーツのスイング軌道上に被る形で、手前または後続に他の色のノーツが配置されているパターン。
 ノーツ同士の間隔やBPMによっては、スイング前の軌道またはスイング後の軌道が別の色のノーツと被ってしまい、巻き込み（バッドカット）の危険性が上がってしまう。
 本来の名称はヒットボックス・ステアケース（Hitbox Staircase）。</t>
@@ -7069,44 +6785,6 @@
   </si>
   <si>
     <t>Flower Note, Star Note</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ノーツを45度違いで重ねて配置したもの。花(?)のような見た目をした特殊な配置。スターノーツともいう。
-色違いや矢印ノーツであれば難度の高い特殊配置だが、同じ色のドットノーツであれば（特殊なことに変わりはないが）使用しやすい。</t>
-    <rPh sb="52" eb="54">
-      <t>イロチガ</t>
-    </rPh>
-    <rPh sb="56" eb="61">
-      <t>ヤジルシ</t>
-    </rPh>
-    <rPh sb="65" eb="67">
-      <t>ナンド</t>
-    </rPh>
-    <rPh sb="68" eb="69">
-      <t>タカ</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>トクシュ</t>
-    </rPh>
-    <rPh sb="72" eb="74">
-      <t>ハイチ</t>
-    </rPh>
-    <rPh sb="77" eb="78">
-      <t>オナ</t>
-    </rPh>
-    <rPh sb="79" eb="80">
-      <t>イロ</t>
-    </rPh>
-    <rPh sb="92" eb="94">
-      <t>トクシュ</t>
-    </rPh>
-    <rPh sb="98" eb="99">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="106" eb="108">
-      <t>シヨウ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -8151,50 +7829,6 @@
     </rPh>
     <rPh sb="228" eb="232">
       <t>サンコウドウガ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>同じ色を同じ方向に連続で切らせる配置。自然な腕の交互の振り（パリティ）を阻害するため、低難易度や特殊な譜面を除いては基本的に避けるべき配置である。ダブルディレクションの略。
-※ボムリセットは直感的なリセットが行える為、DDには含まれない。</t>
-    <rPh sb="2" eb="3">
-      <t>イロ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>ウデ</t>
-    </rPh>
-    <rPh sb="43" eb="47">
-      <t>テイナンイド</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>トクシュ</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>フメン</t>
-    </rPh>
-    <rPh sb="54" eb="55">
-      <t>ノゾ</t>
-    </rPh>
-    <rPh sb="58" eb="61">
-      <t>キホンテキ</t>
-    </rPh>
-    <rPh sb="67" eb="69">
-      <t>ハイチ</t>
-    </rPh>
-    <rPh sb="84" eb="85">
-      <t>リャク</t>
-    </rPh>
-    <rPh sb="95" eb="98">
-      <t>チョッカ</t>
-    </rPh>
-    <rPh sb="104" eb="105">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="107" eb="108">
-      <t>タメ</t>
-    </rPh>
-    <rPh sb="113" eb="114">
-      <t>フク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -10262,6 +9896,340 @@
     <rPh sb="146" eb="147">
       <t>オコナ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>非常に遅いスライダー。ずらし間隔が通常のスライダーより極端に遅く、ゆっくりなぞって切ることを想定した配置である。
+ずらし間隔に明確な決まりはないが、1/8や1/4がよく見受けられる。その遅さもあって通常のスライダーとは違い、スライダーが長かったり、曲げたり、切り替えしたりといったユニークな使い方ができる。ゲームの仕様上遅いスイングでは角度点を出すことが非常に難しい為、一般的な譜面ではほぼ使用されず、特殊な配置といえる。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同じ色を同じ方向に連続で切らせる配置。自然な腕の交互の振り（パリティ）を阻害するため、低難易度や特殊な譜面を除いては基本的に避けるべき配置である。ダブルディレクションの略。
+※ボムリセットは直感的なリセットが行える為、DDには含まれない。
+※高難度テック譜面では、DDのように見えて「リストロールで取ることを前提とした配置」の場合もある。その場合はパリティが繋がる為DDとはならない。</t>
+    <rPh sb="2" eb="3">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ウデ</t>
+    </rPh>
+    <rPh sb="43" eb="47">
+      <t>テイナンイド</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>トクシュ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>フメン</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>ノゾ</t>
+    </rPh>
+    <rPh sb="58" eb="61">
+      <t>キホンテキ</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="84" eb="85">
+      <t>リャク</t>
+    </rPh>
+    <rPh sb="95" eb="98">
+      <t>チョッカ</t>
+    </rPh>
+    <rPh sb="104" eb="105">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="107" eb="108">
+      <t>タメ</t>
+    </rPh>
+    <rPh sb="113" eb="114">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="121" eb="124">
+      <t>コウナンド</t>
+    </rPh>
+    <rPh sb="127" eb="129">
+      <t>フメン</t>
+    </rPh>
+    <rPh sb="138" eb="139">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="149" eb="150">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="154" eb="156">
+      <t>ゼンテイ</t>
+    </rPh>
+    <rPh sb="159" eb="161">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="163" eb="165">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="171" eb="173">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="179" eb="180">
+      <t>ツナ</t>
+    </rPh>
+    <rPh sb="182" eb="183">
+      <t>タメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>片手で、三角形の頂点を辿るように3つのノーツを切らせる配置パターン。
+本質は「パリティが繋がらないフロー」になってしまうことである。参考画像では、斜めノーツをフォアハンド、横ノーツをバックハンドで切った後、3つ目の上向きノーツをフォアハンドで切ることが非常に困難なため、プレイヤーは咄嗟のリセットを余儀なくされる。これは、「その譜面がパリティ通りのスイングを想定してない」為に発生してしまう配置であり、DDと同様、パリティを前提とした通常の譜面では推奨されない。
+※高難度テック譜面では、3つ目を意図的にフォアハンドで切らせる前提で配置される場合があり、この場合はパリティが想定された配置である為トライアングルには該当しない。</t>
+    <rPh sb="248" eb="251">
+      <t>イトテキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NoodleExtensionsを利用し、実際には切れない（判定がない）視覚的な演出として配置されるノーツ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NoodleExtensionsを利用した、触れてもダメージを受けない演出用の壁。
+バニラでも壁の幅を負の値にすることで同様の壁を置くことができるが、本来想定されていない動作である為あまり推奨されない。
+関連: ハイパーウォール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>壁の持続時間（奥行き）を負の値にした壁。通常の壁よりも高速で流れる。
+ゲームの想定されてない挙動である為、基本的には推奨されない。
+関連: フェイクウォール</t>
+    <rPh sb="0" eb="1">
+      <t>カベ</t>
+    </rPh>
+    <rPh sb="2" eb="6">
+      <t>ジゾクジカン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>オクユ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>カベ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ツウジョウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>カベ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>コウソク</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ソウテイ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>キョドウ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>タメ</t>
+    </rPh>
+    <rPh sb="53" eb="56">
+      <t>キホンテキ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>スイショウ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>カンレン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーの顔面に向かって飛んでくる中央2マスいずれかのノーツのこと。プレイヤーの視界を覆ってしまう為、ビジョンブロックの問題を招きやすい。
+それゆえに扱いに注意が必要なノーツであり、このマスにノーツを置く場合にはビジョンブロックの理解と配慮が求められる。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ノーツを45度違いで重ねて配置したもの。花(?)のような見た目をした特殊な配置。スターノーツともいう。
+色違いや矢印ノーツであれば難度の高い特殊配置だが、同じ色のドットノーツであれば（特殊なことに変わりはないが）使用しやすい。
+※同じ色のドットノーツの場合、同じタイミングで重ねると向きが揃ってしまう為、僅かに後ろにずらすことでフラワーの形を維持できる</t>
+    <rPh sb="52" eb="54">
+      <t>イロチガ</t>
+    </rPh>
+    <rPh sb="56" eb="61">
+      <t>ヤジルシ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>ナンド</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>トクシュ</t>
+    </rPh>
+    <rPh sb="72" eb="74">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="77" eb="78">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="79" eb="80">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="92" eb="94">
+      <t>トクシュ</t>
+    </rPh>
+    <rPh sb="98" eb="99">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="106" eb="108">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="115" eb="116">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="117" eb="118">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="126" eb="128">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="129" eb="130">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="137" eb="138">
+      <t>カサ</t>
+    </rPh>
+    <rPh sb="141" eb="142">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="144" eb="145">
+      <t>ソロ</t>
+    </rPh>
+    <rPh sb="150" eb="151">
+      <t>タメ</t>
+    </rPh>
+    <rPh sb="152" eb="153">
+      <t>ワズ</t>
+    </rPh>
+    <rPh sb="155" eb="156">
+      <t>ウシ</t>
+    </rPh>
+    <rPh sb="169" eb="170">
+      <t>カタチ</t>
+    </rPh>
+    <rPh sb="171" eb="173">
+      <t>イジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フュージョン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ノーツを同じ位置・同じタイミングに完全に重なって配置してしまうこと。大抵はコピペミスによって起こるミスマップであり、エディター上では判別しにくい為テストプレイやマップチェッカーでの確認が大事である。
+関連: フュージョン、フラワーノーツ</t>
+    <rPh sb="20" eb="21">
+      <t>カサ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>タイテイ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>ハンベツ</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>タメ</t>
+    </rPh>
+    <rPh sb="90" eb="92">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="93" eb="95">
+      <t>ダイジ</t>
+    </rPh>
+    <rPh sb="100" eb="102">
+      <t>カンレン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>fusion</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">同じ色・同じ方向のノーツが、横に2つ以上並んでいる配置。
+通常のスイングでは取りこぼしてしまう為、ヒットボックスや方向判定の仕組みを応用した切り方が求められる。特殊な配置。ロロッペノーツとも。
+</t>
+    <rPh sb="2" eb="3">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ツウジョウ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>タメ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ホウコウ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>シク</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>オウヨウ</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="74" eb="75">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>トクシュ</t>
+    </rPh>
+    <rPh sb="83" eb="85">
+      <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Fusion, Fused Notes, Hidden Notes</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同じ位置・同じタイミングに2つのノーツを意図して重ねて配置したもの。向きや色を完全に揃えたものから、向きを変えたり、色を変えたりと、重ね方は様々である。いずれにしても特殊な配置である。
+ノーツ＋ボムや、ノーツ＋壁、といった異種のフュージョンも存在する。意図しない重なりであればミスマップであり、マップチェッカーAutoModderではFused objectとして検出される。
+関連: [[スタック（動詞）]]、フラワーノーツ（フュージョンの一種）</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -10407,7 +10375,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -10716,16 +10684,16 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="27.6">
@@ -10739,10 +10707,10 @@
         <v>5</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
@@ -10759,10 +10727,10 @@
         <v>7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
@@ -10776,13 +10744,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>754</v>
+        <v>745</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
@@ -10796,19 +10764,19 @@
         <v>9</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="5"/>
@@ -10821,13 +10789,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>753</v>
+        <v>744</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -10844,10 +10812,10 @@
         <v>12</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
@@ -10861,20 +10829,20 @@
         <v>13</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>784</v>
+        <v>775</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="7" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="55.2">
@@ -10885,20 +10853,20 @@
         <v>14</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>783</v>
+        <v>774</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="7" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="27.6">
@@ -10918,10 +10886,10 @@
         <v>17</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H10" s="9"/>
     </row>
@@ -10933,7 +10901,7 @@
         <v>18</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>19</v>
@@ -10943,7 +10911,7 @@
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H11" s="9"/>
     </row>
@@ -10955,7 +10923,7 @@
         <v>20</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>809</v>
+        <v>799</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>21</v>
@@ -10964,10 +10932,10 @@
         <v>21</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H12" s="1"/>
     </row>
@@ -10979,7 +10947,7 @@
         <v>22</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>23</v>
@@ -10989,7 +10957,7 @@
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H13" s="9"/>
     </row>
@@ -11004,10 +10972,10 @@
         <v>25</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
@@ -11021,13 +10989,13 @@
         <v>26</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
@@ -11041,19 +11009,19 @@
         <v>27</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>797</v>
+        <v>787</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>28</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H16" s="9"/>
     </row>
@@ -11065,13 +11033,13 @@
         <v>29</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>817</v>
+        <v>807</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
@@ -11085,7 +11053,7 @@
         <v>30</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>31</v>
@@ -11094,10 +11062,10 @@
         <v>31</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H18" s="9"/>
     </row>
@@ -11109,7 +11077,7 @@
         <v>32</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>33</v>
@@ -11129,7 +11097,7 @@
         <v>34</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>840</v>
+        <v>830</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>35</v>
@@ -11139,7 +11107,7 @@
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H20" s="9"/>
     </row>
@@ -11151,7 +11119,7 @@
         <v>36</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>762</v>
+        <v>753</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>37</v>
@@ -11161,7 +11129,7 @@
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H21" s="9"/>
     </row>
@@ -11183,7 +11151,7 @@
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H22" s="9"/>
     </row>
@@ -11195,17 +11163,17 @@
         <v>41</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H23" s="9"/>
     </row>
@@ -11217,17 +11185,17 @@
         <v>42</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H24" s="9"/>
     </row>
@@ -11239,19 +11207,19 @@
         <v>44</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H25" s="9"/>
     </row>
@@ -11263,23 +11231,23 @@
         <v>45</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H26" s="9"/>
     </row>
-    <row r="27" spans="1:8" ht="41.4">
+    <row r="27" spans="1:8" ht="69">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -11287,19 +11255,19 @@
         <v>46</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>786</v>
+        <v>850</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>47</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H27" s="9"/>
     </row>
@@ -11311,17 +11279,17 @@
         <v>48</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H28" s="9"/>
     </row>
@@ -11330,16 +11298,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>533</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>580</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>534</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
@@ -11356,10 +11324,10 @@
         <v>50</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
@@ -11373,17 +11341,17 @@
         <v>51</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H31" s="9"/>
     </row>
@@ -11395,17 +11363,17 @@
         <v>52</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H32" s="9"/>
     </row>
@@ -11420,18 +11388,18 @@
         <v>54</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H33" s="9"/>
     </row>
-    <row r="34" spans="1:8" ht="27.6">
+    <row r="34" spans="1:8" ht="55.2">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -11439,17 +11407,17 @@
         <v>55</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>627</v>
+        <v>855</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H34" s="9"/>
     </row>
@@ -11461,21 +11429,21 @@
         <v>56</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>540</v>
+        <v>852</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H35" s="9"/>
     </row>
-    <row r="36" spans="1:8" ht="41.4">
+    <row r="36" spans="1:8" ht="55.2">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -11483,17 +11451,17 @@
         <v>57</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>628</v>
+        <v>853</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H36" s="9"/>
     </row>
@@ -11505,7 +11473,7 @@
         <v>58</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>758</v>
+        <v>749</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>59</v>
@@ -11515,7 +11483,7 @@
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H37" s="9"/>
     </row>
@@ -11530,20 +11498,20 @@
         <v>61</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H38" s="9"/>
     </row>
-    <row r="39" spans="1:8" ht="41.4">
+    <row r="39" spans="1:8" ht="69">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -11551,19 +11519,19 @@
         <v>62</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>751</v>
+        <v>856</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H39" s="9"/>
     </row>
@@ -11575,19 +11543,19 @@
         <v>63</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H40" s="9"/>
     </row>
@@ -11599,7 +11567,7 @@
         <v>64</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>839</v>
+        <v>829</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>65</v>
@@ -11609,7 +11577,7 @@
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H41" s="9"/>
     </row>
@@ -11621,19 +11589,19 @@
         <v>66</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>802</v>
+        <v>792</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H42" s="9"/>
     </row>
@@ -11648,16 +11616,16 @@
         <v>68</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H43" s="9"/>
     </row>
@@ -11669,19 +11637,19 @@
         <v>69</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H44" s="1"/>
     </row>
@@ -11696,14 +11664,14 @@
         <v>71</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H45" s="9"/>
     </row>
@@ -11718,10 +11686,10 @@
         <v>73</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
@@ -11738,10 +11706,10 @@
         <v>75</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
@@ -11755,19 +11723,19 @@
         <v>76</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H48" s="9"/>
     </row>
@@ -11779,16 +11747,16 @@
         <v>77</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="9"/>
@@ -11801,17 +11769,17 @@
         <v>78</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H50" s="9"/>
     </row>
@@ -11823,17 +11791,17 @@
         <v>79</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H51" s="9"/>
     </row>
@@ -11845,7 +11813,7 @@
         <v>80</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>81</v>
@@ -11855,7 +11823,7 @@
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H52" s="9"/>
     </row>
@@ -11870,14 +11838,14 @@
         <v>83</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H53" s="9"/>
     </row>
@@ -11889,21 +11857,21 @@
         <v>84</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H54" s="9"/>
     </row>
-    <row r="55" spans="1:8" ht="27.6">
+    <row r="55" spans="1:8" ht="55.2">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -11911,19 +11879,19 @@
         <v>85</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>591</v>
+        <v>860</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H55" s="9"/>
     </row>
@@ -11932,7 +11900,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>86</v>
@@ -11945,7 +11913,7 @@
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H56" s="9"/>
     </row>
@@ -11954,10 +11922,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>88</v>
@@ -11967,7 +11935,7 @@
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H57" s="9"/>
     </row>
@@ -11979,7 +11947,7 @@
         <v>89</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>90</v>
@@ -11989,7 +11957,7 @@
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H58" s="9"/>
     </row>
@@ -12001,17 +11969,17 @@
         <v>91</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H59" s="9"/>
     </row>
@@ -12020,20 +11988,20 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>806</v>
+        <v>796</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H60" s="9"/>
     </row>
@@ -12042,10 +12010,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>804</v>
+        <v>794</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>92</v>
@@ -12055,7 +12023,7 @@
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H61" s="9"/>
     </row>
@@ -12064,10 +12032,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>93</v>
@@ -12077,7 +12045,7 @@
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H62" s="9"/>
     </row>
@@ -12086,10 +12054,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>94</v>
@@ -12099,7 +12067,7 @@
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H63" s="9"/>
     </row>
@@ -12111,17 +12079,17 @@
         <v>95</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H64" s="9"/>
     </row>
@@ -12133,7 +12101,7 @@
         <v>96</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>820</v>
+        <v>810</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>97</v>
@@ -12153,13 +12121,13 @@
         <v>98</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>819</v>
+        <v>809</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>99</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
@@ -12183,7 +12151,7 @@
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H67" s="9"/>
     </row>
@@ -12205,7 +12173,7 @@
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H68" s="9"/>
     </row>
@@ -12214,20 +12182,20 @@
         <v>68</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>106</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H69" s="9"/>
     </row>
@@ -12239,17 +12207,17 @@
         <v>107</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H70" s="9"/>
     </row>
@@ -12261,20 +12229,20 @@
         <v>108</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="106.8" customHeight="1">
@@ -12285,19 +12253,19 @@
         <v>109</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>814</v>
+        <v>804</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H72" s="9"/>
     </row>
@@ -12309,19 +12277,19 @@
         <v>110</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>815</v>
+        <v>805</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H73" s="9"/>
     </row>
@@ -12333,19 +12301,19 @@
         <v>111</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H74" s="9"/>
     </row>
@@ -12357,7 +12325,7 @@
         <v>112</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>113</v>
@@ -12367,7 +12335,7 @@
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H75" s="9"/>
     </row>
@@ -12379,17 +12347,17 @@
         <v>114</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H76" s="9"/>
     </row>
@@ -12401,13 +12369,13 @@
         <v>115</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3"/>
@@ -12421,17 +12389,17 @@
         <v>116</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H78" s="9"/>
     </row>
@@ -12443,17 +12411,17 @@
         <v>117</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>779</v>
+        <v>770</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H79" s="9"/>
     </row>
@@ -12465,17 +12433,17 @@
         <v>118</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H80" s="9"/>
     </row>
@@ -12497,7 +12465,7 @@
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H81" s="9"/>
     </row>
@@ -12509,17 +12477,17 @@
         <v>122</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H82" s="9"/>
     </row>
@@ -12531,17 +12499,17 @@
         <v>123</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>823</v>
+        <v>813</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H83" s="9"/>
     </row>
@@ -12556,14 +12524,14 @@
         <v>125</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H84" s="9"/>
     </row>
@@ -12578,14 +12546,14 @@
         <v>127</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H85" s="9"/>
     </row>
@@ -12597,19 +12565,19 @@
         <v>128</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>707</v>
+        <v>851</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H86" s="9"/>
     </row>
@@ -12621,17 +12589,17 @@
         <v>129</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H87" s="9"/>
     </row>
@@ -12643,17 +12611,17 @@
         <v>130</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H88" s="9"/>
     </row>
@@ -12668,14 +12636,14 @@
         <v>132</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H89" s="9"/>
     </row>
@@ -12687,19 +12655,19 @@
         <v>133</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H90" s="9"/>
     </row>
@@ -12711,17 +12679,17 @@
         <v>134</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H91" s="9"/>
     </row>
@@ -12733,19 +12701,19 @@
         <v>135</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H92" s="9"/>
     </row>
@@ -12760,14 +12728,14 @@
         <v>137</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H93" s="9"/>
     </row>
@@ -12779,17 +12747,17 @@
         <v>138</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>824</v>
+        <v>814</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H94" s="9"/>
     </row>
@@ -12798,26 +12766,26 @@
         <v>94</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>139</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H95" s="9"/>
     </row>
-    <row r="96" spans="1:8" ht="27.6">
+    <row r="96" spans="1:8" ht="41.4">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -12825,13 +12793,13 @@
         <v>140</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>748</v>
+        <v>858</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3"/>
@@ -12848,10 +12816,10 @@
         <v>142</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3"/>
@@ -12865,13 +12833,13 @@
         <v>143</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3"/>
@@ -12888,10 +12856,10 @@
         <v>145</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3"/>
@@ -12908,16 +12876,16 @@
         <v>147</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H100" s="9"/>
     </row>
@@ -12929,17 +12897,17 @@
         <v>148</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H101" s="9"/>
     </row>
@@ -12951,17 +12919,17 @@
         <v>149</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>807</v>
+        <v>797</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F102" s="3"/>
       <c r="G102" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H102" s="9"/>
     </row>
@@ -12973,20 +12941,20 @@
         <v>150</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H103" s="7" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="104" spans="1:8" ht="41.4">
@@ -12997,19 +12965,19 @@
         <v>151</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H104" s="9"/>
     </row>
@@ -13021,19 +12989,19 @@
         <v>152</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H105" s="9"/>
     </row>
@@ -13045,7 +13013,7 @@
         <v>153</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>154</v>
@@ -13055,7 +13023,7 @@
       </c>
       <c r="F106" s="3"/>
       <c r="G106" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H106" s="9"/>
     </row>
@@ -13067,17 +13035,17 @@
         <v>155</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F107" s="3"/>
       <c r="G107" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H107" s="9"/>
     </row>
@@ -13092,10 +13060,10 @@
         <v>157</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
@@ -13112,10 +13080,10 @@
         <v>159</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F109" s="3"/>
       <c r="G109" s="3"/>
@@ -13129,17 +13097,17 @@
         <v>160</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>791</v>
+        <v>781</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F110" s="3"/>
       <c r="G110" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H110" s="9"/>
     </row>
@@ -13151,17 +13119,17 @@
         <v>161</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>792</v>
+        <v>782</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F111" s="3"/>
       <c r="G111" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H111" s="9"/>
     </row>
@@ -13173,17 +13141,17 @@
         <v>162</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>799</v>
+        <v>789</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F112" s="3"/>
       <c r="G112" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H112" s="9"/>
     </row>
@@ -13195,17 +13163,17 @@
         <v>163</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>798</v>
+        <v>788</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F113" s="3"/>
       <c r="G113" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H113" s="9"/>
     </row>
@@ -13214,20 +13182,20 @@
         <v>113</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F114" s="3"/>
       <c r="G114" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H114" s="9"/>
     </row>
@@ -13239,7 +13207,7 @@
         <v>164</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D115" s="3" t="s">
         <v>165</v>
@@ -13249,7 +13217,7 @@
       </c>
       <c r="F115" s="3"/>
       <c r="G115" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H115" s="9"/>
     </row>
@@ -13261,17 +13229,17 @@
         <v>166</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F116" s="3"/>
       <c r="G116" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H116" s="9"/>
     </row>
@@ -13283,17 +13251,17 @@
         <v>167</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F117" s="3"/>
       <c r="G117" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H117" s="9"/>
     </row>
@@ -13308,14 +13276,14 @@
         <v>169</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F118" s="3"/>
       <c r="G118" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H118" s="9"/>
     </row>
@@ -13337,7 +13305,7 @@
       </c>
       <c r="F119" s="3"/>
       <c r="G119" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H119" s="9"/>
     </row>
@@ -13349,17 +13317,17 @@
         <v>173</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F120" s="3"/>
       <c r="G120" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H120" s="9"/>
     </row>
@@ -13371,17 +13339,17 @@
         <v>174</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="D121" s="3" t="s">
         <v>175</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F121" s="3"/>
       <c r="G121" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H121" s="9"/>
     </row>
@@ -13393,7 +13361,7 @@
         <v>176</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>810</v>
+        <v>800</v>
       </c>
       <c r="D122" s="3" t="s">
         <v>177</v>
@@ -13403,7 +13371,7 @@
       </c>
       <c r="F122" s="3"/>
       <c r="G122" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H122" s="9"/>
     </row>
@@ -13418,16 +13386,16 @@
         <v>179</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E123" s="3" t="s">
         <v>178</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H123" s="9"/>
     </row>
@@ -13439,19 +13407,19 @@
         <v>180</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>180</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H124" s="9"/>
     </row>
@@ -13463,16 +13431,16 @@
         <v>181</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="G125" s="3"/>
       <c r="H125" s="9"/>
@@ -13485,17 +13453,17 @@
         <v>182</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E126" s="3" t="s">
         <v>182</v>
       </c>
       <c r="F126" s="3"/>
       <c r="G126" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H126" s="9"/>
     </row>
@@ -13507,17 +13475,17 @@
         <v>183</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>822</v>
+        <v>812</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F127" s="3"/>
       <c r="G127" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H127" s="9"/>
     </row>
@@ -13532,14 +13500,14 @@
         <v>185</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E128" s="3" t="s">
         <v>184</v>
       </c>
       <c r="F128" s="3"/>
       <c r="G128" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H128" s="9"/>
     </row>
@@ -13551,17 +13519,17 @@
         <v>186</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>793</v>
+        <v>783</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E129" s="3" t="s">
         <v>186</v>
       </c>
       <c r="F129" s="3"/>
       <c r="G129" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H129" s="9"/>
     </row>
@@ -13573,13 +13541,13 @@
         <v>187</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>818</v>
+        <v>808</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F130" s="3"/>
       <c r="G130" s="3"/>
@@ -13593,10 +13561,10 @@
         <v>188</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>776</v>
+        <v>767</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>188</v>
@@ -13616,14 +13584,14 @@
         <v>190</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E132" s="3" t="s">
         <v>189</v>
       </c>
       <c r="F132" s="3"/>
       <c r="G132" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H132" s="9"/>
     </row>
@@ -13635,10 +13603,10 @@
         <v>191</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E133" s="3" t="s">
         <v>191</v>
@@ -13655,17 +13623,17 @@
         <v>192</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>808</v>
+        <v>798</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F134" s="3"/>
       <c r="G134" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H134" s="9"/>
     </row>
@@ -13674,20 +13642,20 @@
         <v>134</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="F135" s="3"/>
       <c r="G135" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H135" s="9"/>
     </row>
@@ -13696,20 +13664,20 @@
         <v>135</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>821</v>
+        <v>811</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="F136" s="3"/>
       <c r="G136" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H136" s="9"/>
     </row>
@@ -13721,20 +13689,20 @@
         <v>193</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>785</v>
+        <v>776</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E137" s="3" t="s">
         <v>193</v>
       </c>
       <c r="F137" s="3"/>
       <c r="G137" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H137" s="7" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="41.4">
@@ -13745,17 +13713,17 @@
         <v>194</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>800</v>
+        <v>790</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E138" s="3" t="s">
         <v>194</v>
       </c>
       <c r="F138" s="3"/>
       <c r="G138" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H138" s="9"/>
     </row>
@@ -13767,17 +13735,17 @@
         <v>195</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>803</v>
+        <v>793</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F139" s="3"/>
       <c r="G139" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H139" s="9"/>
     </row>
@@ -13789,19 +13757,19 @@
         <v>196</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H140" s="9"/>
     </row>
@@ -13813,17 +13781,17 @@
         <v>197</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E141" s="3" t="s">
         <v>197</v>
       </c>
       <c r="F141" s="3"/>
       <c r="G141" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H141" s="9"/>
     </row>
@@ -13838,14 +13806,14 @@
         <v>199</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E142" s="3" t="s">
         <v>198</v>
       </c>
       <c r="F142" s="3"/>
       <c r="G142" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H142" s="9"/>
     </row>
@@ -13857,17 +13825,17 @@
         <v>200</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F143" s="3"/>
       <c r="G143" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H143" s="9"/>
     </row>
@@ -13879,16 +13847,16 @@
         <v>201</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>749</v>
+        <v>741</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="G144" s="3"/>
       <c r="H144" s="9"/>
@@ -13901,17 +13869,17 @@
         <v>202</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E145" s="3" t="s">
         <v>202</v>
       </c>
       <c r="F145" s="3"/>
       <c r="G145" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H145" s="9"/>
     </row>
@@ -13923,17 +13891,17 @@
         <v>203</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E146" s="3" t="s">
         <v>203</v>
       </c>
       <c r="F146" s="3"/>
       <c r="G146" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H146" s="9"/>
     </row>
@@ -13945,17 +13913,17 @@
         <v>204</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>764</v>
+        <v>755</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E147" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F147" s="3"/>
       <c r="G147" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H147" s="9"/>
     </row>
@@ -13967,17 +13935,17 @@
         <v>205</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E148" s="3" t="s">
         <v>205</v>
       </c>
       <c r="F148" s="3"/>
       <c r="G148" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H148" s="9"/>
     </row>
@@ -13989,17 +13957,17 @@
         <v>206</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>774</v>
+        <v>765</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F149" s="3"/>
       <c r="G149" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H149" s="9"/>
     </row>
@@ -14011,17 +13979,17 @@
         <v>207</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F150" s="3"/>
       <c r="G150" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H150" s="9"/>
     </row>
@@ -14033,20 +14001,20 @@
         <v>208</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F151" s="3"/>
       <c r="G151" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H151" s="7" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="152" spans="1:8" ht="27.6">
@@ -14054,16 +14022,16 @@
         <v>151</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>842</v>
+        <v>832</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F152" s="3"/>
       <c r="G152" s="3"/>
@@ -14077,17 +14045,17 @@
         <v>209</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F153" s="3"/>
       <c r="G153" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H153" s="9"/>
     </row>
@@ -14099,17 +14067,17 @@
         <v>210</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>843</v>
+        <v>833</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E154" s="3" t="s">
         <v>210</v>
       </c>
       <c r="F154" s="3"/>
       <c r="G154" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H154" s="9"/>
     </row>
@@ -14121,17 +14089,17 @@
         <v>211</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F155" s="3"/>
       <c r="G155" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H155" s="9"/>
     </row>
@@ -14143,19 +14111,19 @@
         <v>212</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>761</v>
+        <v>752</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H156" s="9"/>
     </row>
@@ -14164,20 +14132,20 @@
         <v>156</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C157" s="3" t="s">
         <v>213</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F157" s="3"/>
       <c r="G157" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H157" s="9"/>
     </row>
@@ -14192,16 +14160,16 @@
         <v>215</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E158" s="3" t="s">
         <v>214</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H158" s="9"/>
     </row>
@@ -14213,19 +14181,19 @@
         <v>216</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F159" s="3"/>
       <c r="G159" s="3"/>
       <c r="H159" s="9"/>
     </row>
-    <row r="160" spans="1:8" ht="27.6">
+    <row r="160" spans="1:8" ht="41.4">
       <c r="A160" s="1">
         <v>159</v>
       </c>
@@ -14233,17 +14201,17 @@
         <v>217</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>218</v>
+        <v>854</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E160" s="3" t="s">
         <v>217</v>
       </c>
       <c r="F160" s="3"/>
       <c r="G160" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H160" s="9"/>
     </row>
@@ -14252,23 +14220,23 @@
         <v>160</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>760</v>
+        <v>751</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F161" s="3"/>
       <c r="G161" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H161" s="9" t="s">
-        <v>759</v>
+        <v>750</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="41.4">
@@ -14276,23 +14244,23 @@
         <v>161</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F162" s="3"/>
       <c r="G162" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H162" s="7" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="27.6">
@@ -14300,20 +14268,20 @@
         <v>162</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>752</v>
+        <v>743</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F163" s="3"/>
       <c r="G163" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H163" s="9"/>
     </row>
@@ -14322,20 +14290,20 @@
         <v>163</v>
       </c>
       <c r="B164" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C164" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C164" s="3" t="s">
-        <v>222</v>
-      </c>
       <c r="D164" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F164" s="3"/>
       <c r="G164" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H164" s="9"/>
     </row>
@@ -14344,22 +14312,22 @@
         <v>164</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H165" s="9"/>
     </row>
@@ -14368,20 +14336,20 @@
         <v>165</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F166" s="3"/>
       <c r="G166" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H166" s="9"/>
     </row>
@@ -14390,20 +14358,20 @@
         <v>166</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F167" s="3"/>
       <c r="G167" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H167" s="9"/>
     </row>
@@ -14412,20 +14380,20 @@
         <v>167</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F168" s="3"/>
       <c r="G168" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H168" s="9"/>
     </row>
@@ -14434,21 +14402,21 @@
         <v>168</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>782</v>
+        <v>773</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F169" s="3"/>
       <c r="G169" s="3"/>
       <c r="H169" s="8" t="s">
-        <v>780</v>
+        <v>771</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="124.2">
@@ -14456,23 +14424,23 @@
         <v>169</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F170" s="3"/>
       <c r="G170" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H170" s="7" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="27.6">
@@ -14480,20 +14448,20 @@
         <v>170</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F171" s="3"/>
       <c r="G171" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H171" s="9"/>
     </row>
@@ -14502,20 +14470,20 @@
         <v>171</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F172" s="3"/>
       <c r="G172" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H172" s="9"/>
     </row>
@@ -14524,20 +14492,20 @@
         <v>172</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="D173" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F173" s="3"/>
       <c r="G173" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H173" s="9"/>
     </row>
@@ -14546,20 +14514,20 @@
         <v>173</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F174" s="3"/>
       <c r="G174" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H174" s="9"/>
     </row>
@@ -14568,20 +14536,20 @@
         <v>174</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F175" s="3"/>
       <c r="G175" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H175" s="9"/>
     </row>
@@ -14590,20 +14558,20 @@
         <v>175</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>789</v>
+        <v>779</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F176" s="3"/>
       <c r="G176" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H176" s="9"/>
     </row>
@@ -14612,20 +14580,20 @@
         <v>176</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>811</v>
+        <v>801</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F177" s="3"/>
       <c r="G177" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H177" s="9"/>
     </row>
@@ -14634,20 +14602,20 @@
         <v>177</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>763</v>
+        <v>754</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F178" s="3"/>
       <c r="G178" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H178" s="9"/>
     </row>
@@ -14656,16 +14624,16 @@
         <v>178</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F179" s="3"/>
       <c r="G179" s="3"/>
@@ -14676,20 +14644,20 @@
         <v>179</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>770</v>
+        <v>761</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F180" s="3"/>
       <c r="G180" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H180" s="9"/>
     </row>
@@ -14698,20 +14666,20 @@
         <v>180</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>769</v>
+        <v>760</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F181" s="3"/>
       <c r="G181" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H181" s="9"/>
     </row>
@@ -14720,20 +14688,20 @@
         <v>181</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>772</v>
+        <v>763</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>773</v>
+        <v>764</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F182" s="3"/>
       <c r="G182" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H182" s="9"/>
     </row>
@@ -14742,20 +14710,20 @@
         <v>182</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>790</v>
+        <v>780</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F183" s="3"/>
       <c r="G183" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H183" s="9"/>
     </row>
@@ -14764,20 +14732,20 @@
         <v>183</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F184" s="3"/>
       <c r="G184" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H184" s="9"/>
     </row>
@@ -14786,20 +14754,20 @@
         <v>184</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F185" s="3"/>
       <c r="G185" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H185" s="9"/>
     </row>
@@ -14808,20 +14776,20 @@
         <v>185</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F186" s="3"/>
       <c r="G186" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H186" s="9"/>
     </row>
@@ -14830,20 +14798,20 @@
         <v>186</v>
       </c>
       <c r="B187" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C187" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="C187" s="3" t="s">
-        <v>241</v>
-      </c>
       <c r="D187" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F187" s="3"/>
       <c r="G187" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H187" s="9"/>
     </row>
@@ -14852,20 +14820,20 @@
         <v>187</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F188" s="3"/>
       <c r="G188" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H188" s="9"/>
     </row>
@@ -14874,22 +14842,22 @@
         <v>188</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H189" s="9"/>
     </row>
@@ -14898,20 +14866,20 @@
         <v>189</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F190" s="3"/>
       <c r="G190" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H190" s="9"/>
     </row>
@@ -14920,20 +14888,20 @@
         <v>190</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="F191" s="3"/>
       <c r="G191" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H191" s="9"/>
     </row>
@@ -14942,20 +14910,20 @@
         <v>191</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>838</v>
+        <v>828</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="F192" s="3"/>
       <c r="G192" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H192" s="9"/>
     </row>
@@ -14964,20 +14932,20 @@
         <v>192</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>778</v>
+        <v>769</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="F193" s="3"/>
       <c r="G193" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H193" s="9"/>
     </row>
@@ -14986,20 +14954,20 @@
         <v>193</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="F194" s="3"/>
       <c r="G194" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H194" s="9"/>
     </row>
@@ -15008,16 +14976,16 @@
         <v>194</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>805</v>
+        <v>795</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="F195" s="3"/>
       <c r="G195" s="3"/>
@@ -15028,42 +14996,42 @@
         <v>195</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="F196" s="3"/>
       <c r="G196" s="3"/>
       <c r="H196" s="9"/>
     </row>
-    <row r="197" spans="1:8" ht="69">
+    <row r="197" spans="1:8" ht="82.8">
       <c r="A197" s="1">
         <v>196</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>689</v>
+        <v>849</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="F197" s="3" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H197" s="9"/>
     </row>
@@ -15072,23 +15040,23 @@
         <v>197</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>775</v>
+        <v>766</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>756</v>
+        <v>747</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="F198" s="3"/>
       <c r="G198" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H198" s="8" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
     </row>
     <row r="199" spans="1:8" ht="41.4">
@@ -15096,20 +15064,20 @@
         <v>198</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>788</v>
+        <v>778</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="F199" s="3"/>
       <c r="G199" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H199" s="9"/>
     </row>
@@ -15118,23 +15086,23 @@
         <v>199</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>794</v>
+        <v>784</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="F200" s="3"/>
       <c r="G200" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H200" s="7" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
     </row>
     <row r="201" spans="1:8" ht="41.4">
@@ -15142,22 +15110,22 @@
         <v>200</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H201" s="9"/>
     </row>
@@ -15166,20 +15134,20 @@
         <v>201</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="F202" s="3"/>
       <c r="G202" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H202" s="9"/>
     </row>
@@ -15188,20 +15156,20 @@
         <v>202</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="F203" s="3"/>
       <c r="G203" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H203" s="9"/>
     </row>
@@ -15210,20 +15178,20 @@
         <v>203</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="F204" s="3"/>
       <c r="G204" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H204" s="9"/>
     </row>
@@ -15232,20 +15200,20 @@
         <v>204</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="F205" s="3"/>
       <c r="G205" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H205" s="9"/>
     </row>
@@ -15254,20 +15222,20 @@
         <v>205</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="F206" s="3"/>
       <c r="G206" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H206" s="9"/>
     </row>
@@ -15276,22 +15244,22 @@
         <v>206</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>841</v>
+        <v>831</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>812</v>
+        <v>802</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H207" s="9"/>
     </row>
@@ -15300,22 +15268,22 @@
         <v>207</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H208" s="9"/>
     </row>
@@ -15324,23 +15292,23 @@
         <v>208</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>796</v>
+        <v>786</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="F209" s="3"/>
       <c r="G209" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H209" s="8" t="s">
-        <v>795</v>
+        <v>785</v>
       </c>
     </row>
     <row r="210" spans="1:8" ht="27.6">
@@ -15348,16 +15316,16 @@
         <v>209</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="F210" s="3"/>
       <c r="G210" s="3"/>
@@ -15368,22 +15336,22 @@
         <v>210</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H211" s="9"/>
     </row>
@@ -15392,20 +15360,20 @@
         <v>211</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>755</v>
+        <v>746</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="F212" s="3"/>
       <c r="G212" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H212" s="9"/>
     </row>
@@ -15414,20 +15382,20 @@
         <v>212</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>813</v>
+        <v>803</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="F213" s="3"/>
       <c r="G213" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H213" s="9"/>
     </row>
@@ -15436,20 +15404,20 @@
         <v>213</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>777</v>
+        <v>768</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="F214" s="3"/>
       <c r="G214" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H214" s="9"/>
     </row>
@@ -15458,23 +15426,23 @@
         <v>214</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="F215" s="3"/>
       <c r="G215" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H215" s="8" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
     </row>
     <row r="216" spans="1:8" ht="124.2">
@@ -15482,25 +15450,25 @@
         <v>215</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>757</v>
+        <v>748</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="F216" s="3" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H216" s="8" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
     </row>
     <row r="217" spans="1:8" ht="41.4">
@@ -15508,22 +15476,22 @@
         <v>216</v>
       </c>
       <c r="B217" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="C217" s="3" t="s">
         <v>825</v>
       </c>
-      <c r="C217" s="3" t="s">
-        <v>835</v>
-      </c>
       <c r="D217" s="3" t="s">
-        <v>830</v>
+        <v>820</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>825</v>
+        <v>815</v>
       </c>
       <c r="F217" s="3" t="s">
-        <v>834</v>
+        <v>824</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H217" s="9"/>
     </row>
@@ -15532,19 +15500,19 @@
         <v>217</v>
       </c>
       <c r="B218" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="C218" s="3" t="s">
         <v>826</v>
       </c>
-      <c r="C218" s="3" t="s">
-        <v>836</v>
-      </c>
       <c r="D218" s="3" t="s">
-        <v>831</v>
+        <v>821</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="F218" s="3" t="s">
-        <v>833</v>
+        <v>823</v>
       </c>
       <c r="G218" s="3"/>
       <c r="H218" s="9"/>
@@ -15554,22 +15522,22 @@
         <v>218</v>
       </c>
       <c r="B219" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="C219" s="3" t="s">
         <v>827</v>
       </c>
-      <c r="C219" s="3" t="s">
-        <v>837</v>
-      </c>
       <c r="D219" s="3" t="s">
-        <v>829</v>
+        <v>819</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>828</v>
+        <v>818</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>832</v>
+        <v>822</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H219" s="9"/>
     </row>
@@ -15578,20 +15546,20 @@
         <v>219</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>844</v>
+        <v>834</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>850</v>
+        <v>840</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>851</v>
+        <v>841</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>844</v>
+        <v>834</v>
       </c>
       <c r="F220" s="3"/>
       <c r="G220" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H220" s="9"/>
     </row>
@@ -15600,20 +15568,20 @@
         <v>220</v>
       </c>
       <c r="B221" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="C221" s="3" t="s">
         <v>845</v>
       </c>
-      <c r="C221" s="3" t="s">
-        <v>855</v>
-      </c>
       <c r="D221" s="3" t="s">
-        <v>852</v>
+        <v>842</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>852</v>
+        <v>842</v>
       </c>
       <c r="F221" s="3"/>
       <c r="G221" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H221" s="9"/>
     </row>
@@ -15622,20 +15590,20 @@
         <v>221</v>
       </c>
       <c r="B222" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="C222" s="3" t="s">
         <v>846</v>
       </c>
-      <c r="C222" s="3" t="s">
-        <v>856</v>
-      </c>
       <c r="D222" s="3" t="s">
-        <v>853</v>
+        <v>843</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>846</v>
+        <v>836</v>
       </c>
       <c r="F222" s="3"/>
       <c r="G222" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H222" s="9"/>
     </row>
@@ -15644,20 +15612,20 @@
         <v>222</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>847</v>
+        <v>837</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>858</v>
+        <v>848</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>854</v>
+        <v>844</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>854</v>
+        <v>844</v>
       </c>
       <c r="F223" s="3"/>
       <c r="G223" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H223" s="9"/>
     </row>
@@ -15666,33 +15634,45 @@
         <v>223</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>848</v>
+        <v>838</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>857</v>
+        <v>847</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>849</v>
+        <v>839</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>849</v>
+        <v>839</v>
       </c>
       <c r="F224" s="3"/>
       <c r="G224" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H224" s="9"/>
     </row>
-    <row r="225" spans="1:8">
+    <row r="225" spans="1:8" ht="69">
       <c r="A225" s="1">
         <v>224</v>
       </c>
-      <c r="B225" s="2"/>
-      <c r="C225" s="3"/>
-      <c r="D225" s="3"/>
-      <c r="E225" s="3"/>
-      <c r="F225" s="3"/>
-      <c r="G225" s="3"/>
+      <c r="B225" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>862</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="E225" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="F225" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="G225" s="3" t="s">
+        <v>535</v>
+      </c>
       <c r="H225" s="9"/>
     </row>
     <row r="226" spans="1:8">
@@ -15843,27 +15823,27 @@
   <sheetData>
     <row r="2" spans="2:2">
       <c r="B2" s="10" t="s">
-        <v>766</v>
+        <v>757</v>
       </c>
     </row>
     <row r="3" spans="2:2">
       <c r="B3" s="10" t="s">
-        <v>767</v>
+        <v>758</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" s="10" t="s">
-        <v>771</v>
+        <v>762</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" s="10" t="s">
-        <v>768</v>
+        <v>759</v>
       </c>
     </row>
     <row r="6" spans="2:2">
       <c r="B6" s="10" t="s">
-        <v>781</v>
+        <v>772</v>
       </c>
     </row>
   </sheetData>

--- a/yougo.xlsx
+++ b/yougo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\Beat Saber\MAIN\GitHub\bs-jpmapping-glossary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D0553A-52CB-4125-A6C9-49E239C6E298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{669D2D9B-88B4-443D-9981-641A28626CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2076" yWindow="984" windowWidth="26088" windowHeight="22092" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6336" yWindow="1404" windowWidth="28392" windowHeight="22092" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="公開用データ" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="863">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="868">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -3660,20 +3660,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>左右のコントローラーが物理的に衝突してしまうこと。またはそれを誘発する危険なノーツ配置（クラッシュ配置）。基本的にはマッパーはそれを避けるべきである。
-≒ハンドクラップ</t>
-    <rPh sb="31" eb="33">
-      <t>ユウハツ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>ハイチ</t>
-    </rPh>
-    <rPh sb="53" eb="56">
-      <t>キホンテキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Crossover Scissor, Pickle</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -4686,36 +4672,6 @@
     <t>URL追加</t>
     <rPh sb="3" eb="5">
       <t>ツイカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ノーツに設定されている「当たり判定」の領域。見た目のサイズより大きめに設定されている。
-画像の赤枠がヒットボックス。紫枠はバッドカット判定が発生する領域。
-※画像はBeatLeaderから</t>
-    <rPh sb="44" eb="46">
-      <t>ガゾウ</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>アカワク</t>
-    </rPh>
-    <rPh sb="58" eb="59">
-      <t>ムラサキ</t>
-    </rPh>
-    <rPh sb="59" eb="60">
-      <t>ワク</t>
-    </rPh>
-    <rPh sb="67" eb="69">
-      <t>ハンテイ</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>ハッセイ</t>
-    </rPh>
-    <rPh sb="74" eb="76">
-      <t>リョウイキ</t>
-    </rPh>
-    <rPh sb="79" eb="81">
-      <t>ガゾウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -10172,9 +10128,76 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t xml:space="preserve">同じ色・同じ方向のノーツが、横に2つ以上並んでいる配置。
+    <t>Fusion, Fused Notes, Hidden Notes</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヒットボックスの乱用</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ノーツのヒットボックスが重なっていたり、塞いでいたり、適切に繋がっていなかったりなど、通常の（見た目通りの）スイングでは切ることが難しいノーツ配置のこと。
+一般的な譜面においては推奨されないが、特殊な譜面では意図的に使用される場合がある。
+※海外用語の「Hitbox Abuse」が元々の言葉。"Abuse"の直訳で「ヒットボックスの悪用」と呼ばれる場合もある。
+関連：パラレルノーツ、フュージョン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Hitbox Abuse</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヒットボックスノランヨウ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>hitboxabuse</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ノーツに設定されている「当たり判定」の領域。見た目のサイズより大きめに設定されている。
+画像の赤枠がヒットボックス。紫枠はバッドカット判定が発生する領域。
+※画像はBeatLeaderから
+関連：ヒットボックスの乱用</t>
+    <rPh sb="44" eb="46">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>アカワク</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>ムラサキ</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>ワク</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>リョウイキ</t>
+    </rPh>
+    <rPh sb="79" eb="81">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="95" eb="97">
+      <t>カンレン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同じ位置・同じタイミングに2つのノーツを意図して重ねて配置したもの。向きや色を完全に揃えたものから、向きを変えたり、色を変えたりと、重ね方は様々である。いずれにしても特殊な配置である。
+ノーツ＋ボムや、ノーツ＋壁、といった異種のフュージョンも存在する。意図しない重なりであればミスマップであり、マップチェッカーAutoModderではFused objectとして検出される。
+関連: [[スタック（動詞）]]、フラワーノーツ（フュージョンの一種）、ヒットボックスの乱用</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同じ色・同じ方向のノーツが、横に2つ以上並んでいる配置。
 通常のスイングでは取りこぼしてしまう為、ヒットボックスや方向判定の仕組みを応用した切り方が求められる。特殊な配置。ロロッペノーツとも。
-</t>
+関連：ヒットボックスの乱用</t>
     <rPh sb="2" eb="3">
       <t>イロ</t>
     </rPh>
@@ -10220,16 +10243,21 @@
     <rPh sb="83" eb="85">
       <t>ハイチ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Fusion, Fused Notes, Hidden Notes</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>同じ位置・同じタイミングに2つのノーツを意図して重ねて配置したもの。向きや色を完全に揃えたものから、向きを変えたり、色を変えたりと、重ね方は様々である。いずれにしても特殊な配置である。
-ノーツ＋ボムや、ノーツ＋壁、といった異種のフュージョンも存在する。意図しない重なりであればミスマップであり、マップチェッカーAutoModderではFused objectとして検出される。
-関連: [[スタック（動詞）]]、フラワーノーツ（フュージョンの一種）</t>
+    <rPh sb="97" eb="99">
+      <t>カンレン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左右のコントローラーが物理的に衝突してしまうこと。またはそれを誘発する危険なノーツ配置（クラッシュ配置）。
+一般的にはクロス配置などの手が交差する状況下でクラッシュの可能性が上がりやすいが、配置の形や譜面の難易度感、セットアップの有無、プレイヤーレベルなどによってもその安全・危険度合いは大きく変わってくる。
+≒ハンドクラップ</t>
+    <rPh sb="95" eb="97">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="98" eb="99">
+      <t>カタチ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -10375,7 +10403,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -10693,7 +10721,7 @@
         <v>534</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="27.6">
@@ -10744,7 +10772,7 @@
         <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>381</v>
@@ -10764,7 +10792,7 @@
         <v>9</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>382</v>
@@ -10789,7 +10817,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>383</v>
@@ -10829,7 +10857,7 @@
         <v>13</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>385</v>
@@ -10838,11 +10866,11 @@
         <v>247</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="7" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="55.2">
@@ -10853,7 +10881,7 @@
         <v>14</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>386</v>
@@ -10862,11 +10890,11 @@
         <v>254</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="7" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="27.6">
@@ -10901,7 +10929,7 @@
         <v>18</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>19</v>
@@ -10923,7 +10951,7 @@
         <v>20</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>21</v>
@@ -10947,7 +10975,7 @@
         <v>22</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>23</v>
@@ -10989,7 +11017,7 @@
         <v>26</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>388</v>
@@ -11009,7 +11037,7 @@
         <v>27</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>389</v>
@@ -11033,7 +11061,7 @@
         <v>29</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>390</v>
@@ -11077,7 +11105,7 @@
         <v>32</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>33</v>
@@ -11097,7 +11125,7 @@
         <v>34</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>35</v>
@@ -11119,7 +11147,7 @@
         <v>36</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>37</v>
@@ -11155,7 +11183,7 @@
       </c>
       <c r="H22" s="9"/>
     </row>
-    <row r="23" spans="1:8" ht="41.4">
+    <row r="23" spans="1:8" ht="69">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -11163,7 +11191,7 @@
         <v>41</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>575</v>
+        <v>867</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>391</v>
@@ -11185,10 +11213,10 @@
         <v>42</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>317</v>
@@ -11207,7 +11235,7 @@
         <v>44</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>378</v>
@@ -11231,10 +11259,10 @@
         <v>45</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>249</v>
@@ -11255,7 +11283,7 @@
         <v>46</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>318</v>
@@ -11279,7 +11307,7 @@
         <v>48</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>392</v>
@@ -11301,7 +11329,7 @@
         <v>532</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>392</v>
@@ -11341,7 +11369,7 @@
         <v>51</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>394</v>
@@ -11407,7 +11435,7 @@
         <v>55</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>398</v>
@@ -11429,7 +11457,7 @@
         <v>56</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>400</v>
@@ -11451,7 +11479,7 @@
         <v>57</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>399</v>
@@ -11473,7 +11501,7 @@
         <v>58</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>59</v>
@@ -11519,10 +11547,10 @@
         <v>62</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>265</v>
@@ -11543,7 +11571,7 @@
         <v>63</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>402</v>
@@ -11567,7 +11595,7 @@
         <v>64</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>65</v>
@@ -11589,7 +11617,7 @@
         <v>66</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>403</v>
@@ -11629,7 +11657,7 @@
       </c>
       <c r="H43" s="9"/>
     </row>
-    <row r="44" spans="1:8" ht="41.4">
+    <row r="44" spans="1:8" ht="55.2">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -11637,7 +11665,7 @@
         <v>69</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>620</v>
+        <v>864</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>405</v>
@@ -11747,7 +11775,7 @@
         <v>77</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>410</v>
@@ -11769,7 +11797,7 @@
         <v>78</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>321</v>
@@ -11791,7 +11819,7 @@
         <v>79</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>411</v>
@@ -11813,7 +11841,7 @@
         <v>80</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>81</v>
@@ -11857,7 +11885,7 @@
         <v>84</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>413</v>
@@ -11879,7 +11907,7 @@
         <v>85</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>414</v>
@@ -11925,7 +11953,7 @@
         <v>539</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>88</v>
@@ -11947,7 +11975,7 @@
         <v>89</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>90</v>
@@ -11969,7 +11997,7 @@
         <v>91</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>415</v>
@@ -11991,10 +12019,10 @@
         <v>540</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>323</v>
@@ -12013,7 +12041,7 @@
         <v>544</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>92</v>
@@ -12032,10 +12060,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>93</v>
@@ -12054,10 +12082,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>94</v>
@@ -12079,7 +12107,7 @@
         <v>95</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>416</v>
@@ -12101,7 +12129,7 @@
         <v>96</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>97</v>
@@ -12121,7 +12149,7 @@
         <v>98</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>99</v>
@@ -12207,7 +12235,7 @@
         <v>107</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>418</v>
@@ -12229,7 +12257,7 @@
         <v>108</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>419</v>
@@ -12242,7 +12270,7 @@
         <v>535</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="106.8" customHeight="1">
@@ -12253,7 +12281,7 @@
         <v>109</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>420</v>
@@ -12277,7 +12305,7 @@
         <v>110</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>421</v>
@@ -12347,7 +12375,7 @@
         <v>114</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>423</v>
@@ -12369,7 +12397,7 @@
         <v>115</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>424</v>
@@ -12389,7 +12417,7 @@
         <v>116</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>327</v>
@@ -12411,7 +12439,7 @@
         <v>117</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>426</v>
@@ -12433,7 +12461,7 @@
         <v>118</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>425</v>
@@ -12477,7 +12505,7 @@
         <v>122</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>427</v>
@@ -12499,7 +12527,7 @@
         <v>123</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>428</v>
@@ -12565,7 +12593,7 @@
         <v>128</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>431</v>
@@ -12589,7 +12617,7 @@
         <v>129</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>432</v>
@@ -12611,7 +12639,7 @@
         <v>130</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>43</v>
@@ -12655,7 +12683,7 @@
         <v>133</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>434</v>
@@ -12679,7 +12707,7 @@
         <v>134</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>435</v>
@@ -12701,7 +12729,7 @@
         <v>135</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>436</v>
@@ -12747,7 +12775,7 @@
         <v>138</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>438</v>
@@ -12793,7 +12821,7 @@
         <v>140</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>440</v>
@@ -12833,10 +12861,10 @@
         <v>143</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>299</v>
@@ -12897,7 +12925,7 @@
         <v>148</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>444</v>
@@ -12919,7 +12947,7 @@
         <v>149</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>445</v>
@@ -12941,7 +12969,7 @@
         <v>150</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>446</v>
@@ -12954,7 +12982,7 @@
         <v>535</v>
       </c>
       <c r="H103" s="7" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="104" spans="1:8" ht="41.4">
@@ -13013,7 +13041,7 @@
         <v>153</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>154</v>
@@ -13035,7 +13063,7 @@
         <v>155</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>336</v>
@@ -13097,7 +13125,7 @@
         <v>160</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>451</v>
@@ -13119,7 +13147,7 @@
         <v>161</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>452</v>
@@ -13141,7 +13169,7 @@
         <v>162</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>453</v>
@@ -13163,7 +13191,7 @@
         <v>163</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="D113" s="3" t="s">
         <v>454</v>
@@ -13229,7 +13257,7 @@
         <v>166</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D116" s="3" t="s">
         <v>338</v>
@@ -13251,7 +13279,7 @@
         <v>167</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D117" s="3" t="s">
         <v>339</v>
@@ -13317,7 +13345,7 @@
         <v>173</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D120" s="3" t="s">
         <v>455</v>
@@ -13339,7 +13367,7 @@
         <v>174</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D121" s="3" t="s">
         <v>175</v>
@@ -13361,7 +13389,7 @@
         <v>176</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="D122" s="3" t="s">
         <v>177</v>
@@ -13407,7 +13435,7 @@
         <v>180</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>457</v>
@@ -13431,7 +13459,7 @@
         <v>181</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D125" s="3" t="s">
         <v>458</v>
@@ -13475,7 +13503,7 @@
         <v>183</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="D127" s="3" t="s">
         <v>460</v>
@@ -13519,7 +13547,7 @@
         <v>186</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="D129" s="3" t="s">
         <v>462</v>
@@ -13541,10 +13569,10 @@
         <v>187</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="E130" s="3" t="s">
         <v>343</v>
@@ -13561,7 +13589,7 @@
         <v>188</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="D131" s="3" t="s">
         <v>463</v>
@@ -13603,7 +13631,7 @@
         <v>191</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="D133" s="3" t="s">
         <v>465</v>
@@ -13623,7 +13651,7 @@
         <v>192</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="D134" s="3" t="s">
         <v>344</v>
@@ -13645,7 +13673,7 @@
         <v>549</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D135" s="3" t="s">
         <v>550</v>
@@ -13664,16 +13692,16 @@
         <v>135</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="F136" s="3"/>
       <c r="G136" s="3" t="s">
@@ -13689,7 +13717,7 @@
         <v>193</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D137" s="3" t="s">
         <v>466</v>
@@ -13702,7 +13730,7 @@
         <v>535</v>
       </c>
       <c r="H137" s="7" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="41.4">
@@ -13713,7 +13741,7 @@
         <v>194</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="D138" s="3" t="s">
         <v>467</v>
@@ -13735,7 +13763,7 @@
         <v>195</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="D139" s="3" t="s">
         <v>345</v>
@@ -13825,7 +13853,7 @@
         <v>200</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="D143" s="3" t="s">
         <v>346</v>
@@ -13847,7 +13875,7 @@
         <v>201</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="D144" s="3" t="s">
         <v>471</v>
@@ -13891,7 +13919,7 @@
         <v>203</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D146" s="3" t="s">
         <v>473</v>
@@ -13913,7 +13941,7 @@
         <v>204</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D147" s="3" t="s">
         <v>474</v>
@@ -13957,7 +13985,7 @@
         <v>206</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D149" s="3" t="s">
         <v>348</v>
@@ -13979,7 +14007,7 @@
         <v>207</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D150" s="3" t="s">
         <v>476</v>
@@ -14001,7 +14029,7 @@
         <v>208</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="D151" s="3" t="s">
         <v>350</v>
@@ -14014,7 +14042,7 @@
         <v>535</v>
       </c>
       <c r="H151" s="7" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="152" spans="1:8" ht="27.6">
@@ -14025,7 +14053,7 @@
         <v>478</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="D152" s="3" t="s">
         <v>477</v>
@@ -14067,7 +14095,7 @@
         <v>210</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="D154" s="3" t="s">
         <v>479</v>
@@ -14089,7 +14117,7 @@
         <v>211</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D155" s="3" t="s">
         <v>480</v>
@@ -14111,7 +14139,7 @@
         <v>212</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="D156" s="3" t="s">
         <v>481</v>
@@ -14181,7 +14209,7 @@
         <v>216</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D159" s="3" t="s">
         <v>483</v>
@@ -14201,7 +14229,7 @@
         <v>217</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="D160" s="3" t="s">
         <v>484</v>
@@ -14223,7 +14251,7 @@
         <v>218</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="D161" s="3" t="s">
         <v>485</v>
@@ -14236,7 +14264,7 @@
         <v>535</v>
       </c>
       <c r="H161" s="9" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="41.4">
@@ -14247,7 +14275,7 @@
         <v>356</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="D162" s="3" t="s">
         <v>486</v>
@@ -14260,7 +14288,7 @@
         <v>535</v>
       </c>
       <c r="H162" s="7" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="27.6">
@@ -14271,7 +14299,7 @@
         <v>219</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="D163" s="3" t="s">
         <v>357</v>
@@ -14315,7 +14343,7 @@
         <v>222</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D165" s="3" t="s">
         <v>359</v>
@@ -14336,7 +14364,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C166" s="3" t="s">
         <v>223</v>
@@ -14361,7 +14389,7 @@
         <v>224</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D167" s="3" t="s">
         <v>361</v>
@@ -14383,10 +14411,10 @@
         <v>225</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="E168" s="3" t="s">
         <v>225</v>
@@ -14402,10 +14430,10 @@
         <v>168</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="D169" s="3" t="s">
         <v>396</v>
@@ -14416,7 +14444,7 @@
       <c r="F169" s="3"/>
       <c r="G169" s="3"/>
       <c r="H169" s="8" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="124.2">
@@ -14427,7 +14455,7 @@
         <v>362</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="D170" s="3" t="s">
         <v>487</v>
@@ -14440,7 +14468,7 @@
         <v>535</v>
       </c>
       <c r="H170" s="7" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="27.6">
@@ -14473,7 +14501,7 @@
         <v>227</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D172" s="3" t="s">
         <v>488</v>
@@ -14495,7 +14523,7 @@
         <v>228</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D173" s="3" t="s">
         <v>43</v>
@@ -14517,7 +14545,7 @@
         <v>229</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D174" s="3" t="s">
         <v>489</v>
@@ -14536,7 +14564,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C175" s="3" t="s">
         <v>572</v>
@@ -14561,7 +14589,7 @@
         <v>230</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="D176" s="3" t="s">
         <v>491</v>
@@ -14583,7 +14611,7 @@
         <v>231</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D177" s="3" t="s">
         <v>492</v>
@@ -14605,7 +14633,7 @@
         <v>232</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="D178" s="3" t="s">
         <v>494</v>
@@ -14627,7 +14655,7 @@
         <v>233</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D179" s="3" t="s">
         <v>493</v>
@@ -14647,7 +14675,7 @@
         <v>234</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D180" s="3" t="s">
         <v>495</v>
@@ -14669,7 +14697,7 @@
         <v>235</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D181" s="3" t="s">
         <v>496</v>
@@ -14688,10 +14716,10 @@
         <v>181</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="D182" s="3" t="s">
         <v>369</v>
@@ -14710,10 +14738,10 @@
         <v>182</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="D183" s="3" t="s">
         <v>370</v>
@@ -14779,7 +14807,7 @@
         <v>238</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="D186" s="3" t="s">
         <v>373</v>
@@ -14823,7 +14851,7 @@
         <v>241</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="D188" s="3" t="s">
         <v>375</v>
@@ -14842,13 +14870,13 @@
         <v>188</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="E189" s="3" t="s">
         <v>376</v>
@@ -14869,7 +14897,7 @@
         <v>242</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="D190" s="3" t="s">
         <v>377</v>
@@ -14913,7 +14941,7 @@
         <v>531</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="D192" s="3" t="s">
         <v>554</v>
@@ -14932,10 +14960,10 @@
         <v>192</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="D193" s="3" t="s">
         <v>556</v>
@@ -14976,16 +15004,16 @@
         <v>194</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="F195" s="3"/>
       <c r="G195" s="3"/>
@@ -14996,16 +15024,16 @@
         <v>195</v>
       </c>
       <c r="B196" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="D196" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="C196" s="3" t="s">
-        <v>627</v>
-      </c>
-      <c r="D196" s="3" t="s">
+      <c r="E196" s="3" t="s">
         <v>607</v>
-      </c>
-      <c r="E196" s="3" t="s">
-        <v>608</v>
       </c>
       <c r="F196" s="3"/>
       <c r="G196" s="3"/>
@@ -15016,19 +15044,19 @@
         <v>196</v>
       </c>
       <c r="B197" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>847</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="E197" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="F197" s="3" t="s">
         <v>638</v>
-      </c>
-      <c r="C197" s="3" t="s">
-        <v>849</v>
-      </c>
-      <c r="D197" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="E197" s="3" t="s">
-        <v>638</v>
-      </c>
-      <c r="F197" s="3" t="s">
-        <v>640</v>
       </c>
       <c r="G197" s="3" t="s">
         <v>535</v>
@@ -15040,23 +15068,23 @@
         <v>197</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="F198" s="3"/>
       <c r="G198" s="3" t="s">
         <v>535</v>
       </c>
       <c r="H198" s="8" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="199" spans="1:8" ht="41.4">
@@ -15064,16 +15092,16 @@
         <v>198</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="F199" s="3"/>
       <c r="G199" s="3" t="s">
@@ -15086,23 +15114,23 @@
         <v>199</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="F200" s="3"/>
       <c r="G200" s="3" t="s">
         <v>535</v>
       </c>
       <c r="H200" s="7" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="201" spans="1:8" ht="41.4">
@@ -15110,19 +15138,19 @@
         <v>200</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="G201" s="3" t="s">
         <v>535</v>
@@ -15134,16 +15162,16 @@
         <v>201</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="F202" s="3"/>
       <c r="G202" s="3" t="s">
@@ -15156,16 +15184,16 @@
         <v>202</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="F203" s="3"/>
       <c r="G203" s="3" t="s">
@@ -15178,16 +15206,16 @@
         <v>203</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="F204" s="3"/>
       <c r="G204" s="3" t="s">
@@ -15200,16 +15228,16 @@
         <v>204</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="F205" s="3"/>
       <c r="G205" s="3" t="s">
@@ -15222,16 +15250,16 @@
         <v>205</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="F206" s="3"/>
       <c r="G206" s="3" t="s">
@@ -15244,19 +15272,19 @@
         <v>206</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="G207" s="3" t="s">
         <v>535</v>
@@ -15268,19 +15296,19 @@
         <v>207</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="G208" s="3" t="s">
         <v>535</v>
@@ -15292,23 +15320,23 @@
         <v>208</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="F209" s="3"/>
       <c r="G209" s="3" t="s">
         <v>535</v>
       </c>
       <c r="H209" s="8" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="210" spans="1:8" ht="27.6">
@@ -15316,16 +15344,16 @@
         <v>209</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="F210" s="3"/>
       <c r="G210" s="3"/>
@@ -15336,19 +15364,19 @@
         <v>210</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="G211" s="3" t="s">
         <v>535</v>
@@ -15360,16 +15388,16 @@
         <v>211</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="F212" s="3"/>
       <c r="G212" s="3" t="s">
@@ -15382,16 +15410,16 @@
         <v>212</v>
       </c>
       <c r="B213" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>801</v>
+      </c>
+      <c r="D213" s="3" t="s">
         <v>686</v>
       </c>
-      <c r="C213" s="3" t="s">
-        <v>803</v>
-      </c>
-      <c r="D213" s="3" t="s">
-        <v>688</v>
-      </c>
       <c r="E213" s="3" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="F213" s="3"/>
       <c r="G213" s="3" t="s">
@@ -15404,16 +15432,16 @@
         <v>213</v>
       </c>
       <c r="B214" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="D214" s="3" t="s">
         <v>687</v>
       </c>
-      <c r="C214" s="3" t="s">
-        <v>768</v>
-      </c>
-      <c r="D214" s="3" t="s">
-        <v>689</v>
-      </c>
       <c r="E214" s="3" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="F214" s="3"/>
       <c r="G214" s="3" t="s">
@@ -15426,23 +15454,23 @@
         <v>214</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="F215" s="3"/>
       <c r="G215" s="3" t="s">
         <v>535</v>
       </c>
       <c r="H215" s="8" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
     </row>
     <row r="216" spans="1:8" ht="124.2">
@@ -15450,25 +15478,25 @@
         <v>215</v>
       </c>
       <c r="B216" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="C216" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="D216" s="3" t="s">
         <v>726</v>
       </c>
-      <c r="C216" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="D216" s="3" t="s">
+      <c r="E216" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="F216" s="3" t="s">
         <v>728</v>
       </c>
-      <c r="E216" s="3" t="s">
+      <c r="G216" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="H216" s="8" t="s">
         <v>727</v>
-      </c>
-      <c r="F216" s="3" t="s">
-        <v>730</v>
-      </c>
-      <c r="G216" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="H216" s="8" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="217" spans="1:8" ht="41.4">
@@ -15476,19 +15504,19 @@
         <v>216</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="F217" s="3" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="G217" s="3" t="s">
         <v>535</v>
@@ -15500,19 +15528,19 @@
         <v>217</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="D218" s="3" t="s">
+        <v>819</v>
+      </c>
+      <c r="E218" s="3" t="s">
+        <v>814</v>
+      </c>
+      <c r="F218" s="3" t="s">
         <v>821</v>
-      </c>
-      <c r="E218" s="3" t="s">
-        <v>816</v>
-      </c>
-      <c r="F218" s="3" t="s">
-        <v>823</v>
       </c>
       <c r="G218" s="3"/>
       <c r="H218" s="9"/>
@@ -15522,19 +15550,19 @@
         <v>218</v>
       </c>
       <c r="B219" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>825</v>
+      </c>
+      <c r="D219" s="3" t="s">
         <v>817</v>
       </c>
-      <c r="C219" s="3" t="s">
-        <v>827</v>
-      </c>
-      <c r="D219" s="3" t="s">
-        <v>819</v>
-      </c>
       <c r="E219" s="3" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="G219" s="3" t="s">
         <v>535</v>
@@ -15546,16 +15574,16 @@
         <v>219</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="F220" s="3"/>
       <c r="G220" s="3" t="s">
@@ -15568,16 +15596,16 @@
         <v>220</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="F221" s="3"/>
       <c r="G221" s="3" t="s">
@@ -15590,16 +15618,16 @@
         <v>221</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="F222" s="3"/>
       <c r="G222" s="3" t="s">
@@ -15612,16 +15640,16 @@
         <v>222</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="F223" s="3"/>
       <c r="G223" s="3" t="s">
@@ -15634,16 +15662,16 @@
         <v>223</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="F224" s="3"/>
       <c r="G224" s="3" t="s">
@@ -15656,35 +15684,47 @@
         <v>224</v>
       </c>
       <c r="B225" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>858</v>
+      </c>
+      <c r="E225" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="F225" s="3" t="s">
         <v>857</v>
       </c>
-      <c r="C225" s="3" t="s">
-        <v>862</v>
-      </c>
-      <c r="D225" s="3" t="s">
-        <v>861</v>
-      </c>
-      <c r="E225" s="3" t="s">
-        <v>857</v>
-      </c>
-      <c r="F225" s="3" t="s">
-        <v>859</v>
-      </c>
       <c r="G225" s="3" t="s">
         <v>535</v>
       </c>
       <c r="H225" s="9"/>
     </row>
-    <row r="226" spans="1:8">
+    <row r="226" spans="1:8" ht="82.8">
       <c r="A226" s="1">
         <v>225</v>
       </c>
-      <c r="B226" s="2"/>
-      <c r="C226" s="3"/>
-      <c r="D226" s="3"/>
-      <c r="E226" s="3"/>
-      <c r="F226" s="3"/>
-      <c r="G226" s="3"/>
+      <c r="B226" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="E226" s="3" t="s">
+        <v>862</v>
+      </c>
+      <c r="F226" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="G226" s="3" t="s">
+        <v>535</v>
+      </c>
       <c r="H226" s="9"/>
     </row>
     <row r="227" spans="1:8">
@@ -15823,27 +15863,27 @@
   <sheetData>
     <row r="2" spans="2:2">
       <c r="B2" s="10" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
     </row>
     <row r="3" spans="2:2">
       <c r="B3" s="10" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" s="10" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" s="10" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
     </row>
     <row r="6" spans="2:2">
       <c r="B6" s="10" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
   </sheetData>
